--- a/점포별_공용알바_공제매입처_리스트.xlsx
+++ b/점포별_공용알바_공제매입처_리스트.xlsx
@@ -408,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G156"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -3883,35 +3883,131 @@
         <v>N</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" s="1">
+        <v>49</v>
+      </c>
+      <c r="B152" s="1" t="str">
+        <v>문구</v>
+      </c>
+      <c r="C152" s="1" t="str">
+        <v>0803176</v>
+      </c>
+      <c r="D152" s="1" t="str">
+        <v>라이브워크</v>
+      </c>
+      <c r="E152" s="1" t="str">
+        <v>IC0317600</v>
+      </c>
+      <c r="F152" s="1" t="str">
+        <v>라이브워크 일반</v>
+      </c>
+      <c r="G152" s="1" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1">
+        <v>50</v>
+      </c>
+      <c r="B153" s="1" t="str">
+        <v>문구</v>
+      </c>
+      <c r="C153" s="1" t="str">
+        <v>0817560</v>
+      </c>
+      <c r="D153" s="1" t="str">
+        <v>도나앤데코</v>
+      </c>
+      <c r="E153" s="1" t="str">
+        <v>IC0756000</v>
+      </c>
+      <c r="F153" s="1" t="str">
+        <v>도나앤데코 일반</v>
+      </c>
+      <c r="G153" s="1" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1">
+        <v>51</v>
+      </c>
+      <c r="B154" s="1" t="str">
+        <v>문구</v>
+      </c>
+      <c r="C154" s="1" t="str">
+        <v>0806606</v>
+      </c>
+      <c r="D154" s="1" t="str">
+        <v>디자인랩(레더랩)</v>
+      </c>
+      <c r="E154" s="1" t="str">
+        <v>IC0660600</v>
+      </c>
+      <c r="F154" s="1" t="str">
+        <v>디자인랩(레더랩) 일반</v>
+      </c>
+      <c r="G154" s="1" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1">
+        <v>52</v>
+      </c>
+      <c r="B155" s="1" t="str">
+        <v>문구</v>
+      </c>
+      <c r="C155" s="1" t="str">
+        <v>0803229</v>
+      </c>
+      <c r="D155" s="1" t="str">
+        <v>웨이크업(wakup)</v>
+      </c>
+      <c r="E155" s="1" t="str">
+        <v>IC0322900</v>
+      </c>
+      <c r="F155" s="1" t="str">
+        <v>웨이크업(wakup) 일반</v>
+      </c>
+      <c r="G155" s="1" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1">
+        <v>53</v>
+      </c>
+      <c r="B156" s="1" t="str">
+        <v>문구</v>
+      </c>
+      <c r="C156" s="1" t="str">
+        <v>0803288</v>
+      </c>
+      <c r="D156" s="1" t="str">
+        <v>명성코리아</v>
+      </c>
+      <c r="E156" s="1" t="str">
+        <v>IC0328800</v>
+      </c>
+      <c r="F156" s="1" t="str">
+        <v>명성코리아 일반</v>
+      </c>
+      <c r="G156" s="1" t="str">
+        <v>Y</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G151"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G156"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q151"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" customWidth="1"/>
-    <col min="11" max="11" width="13.83203125" customWidth="1"/>
-    <col min="12" max="12" width="13.83203125" customWidth="1"/>
-    <col min="13" max="13" width="13.83203125" customWidth="1"/>
-    <col min="14" max="14" width="13.83203125" customWidth="1"/>
-    <col min="15" max="15" width="13.83203125" customWidth="1"/>
-    <col min="16" max="16" width="13.83203125" customWidth="1"/>
-    <col min="17" max="17" width="13.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:Q156"/>
   <sheetData>
     <row r="1" xml:space="preserve">
       <c r="A1" s="1" t="str">
@@ -11926,9 +12022,274 @@
         <v>750000</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152" s="1" t="str">
+        <v>0803176</v>
+      </c>
+      <c r="C152" s="1" t="str">
+        <v>라이브워크</v>
+      </c>
+      <c r="D152" s="1" t="str">
+        <v>문구</v>
+      </c>
+      <c r="E152" s="1" t="str">
+        <v>IC0317600</v>
+      </c>
+      <c r="F152" s="1" t="str">
+        <v>라이브워크 일반</v>
+      </c>
+      <c r="G152" s="1">
+        <v>0</v>
+      </c>
+      <c r="H152" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I152" s="1">
+        <v>0</v>
+      </c>
+      <c r="J152" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K152" s="1">
+        <v>0</v>
+      </c>
+      <c r="L152" s="1" t="str">
+        <v/>
+      </c>
+      <c r="M152" s="1">
+        <v>0</v>
+      </c>
+      <c r="N152" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O152" s="1">
+        <v>2223710</v>
+      </c>
+      <c r="P152" s="1" t="str">
+        <v/>
+      </c>
+      <c r="Q152" s="1">
+        <v>2223710</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153" s="1" t="str">
+        <v>0817560</v>
+      </c>
+      <c r="C153" s="1" t="str">
+        <v>도나앤데코</v>
+      </c>
+      <c r="D153" s="1" t="str">
+        <v>문구</v>
+      </c>
+      <c r="E153" s="1" t="str">
+        <v>IC0756000</v>
+      </c>
+      <c r="F153" s="1" t="str">
+        <v>도나앤데코 일반</v>
+      </c>
+      <c r="G153" s="1">
+        <v>0</v>
+      </c>
+      <c r="H153" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I153" s="1">
+        <v>0</v>
+      </c>
+      <c r="J153" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K153" s="1">
+        <v>0</v>
+      </c>
+      <c r="L153" s="1" t="str">
+        <v/>
+      </c>
+      <c r="M153" s="1">
+        <v>0</v>
+      </c>
+      <c r="N153" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O153" s="1">
+        <v>1429400</v>
+      </c>
+      <c r="P153" s="1" t="str">
+        <v/>
+      </c>
+      <c r="Q153" s="1">
+        <v>1429400</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154" s="1" t="str">
+        <v>0806606</v>
+      </c>
+      <c r="C154" s="1" t="str">
+        <v>디자인랩(레더랩)</v>
+      </c>
+      <c r="D154" s="1" t="str">
+        <v>문구</v>
+      </c>
+      <c r="E154" s="1" t="str">
+        <v>IC0660600</v>
+      </c>
+      <c r="F154" s="1" t="str">
+        <v>디자인랩(레더랩) 일반</v>
+      </c>
+      <c r="G154" s="1">
+        <v>0</v>
+      </c>
+      <c r="H154" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I154" s="1">
+        <v>0</v>
+      </c>
+      <c r="J154" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K154" s="1">
+        <v>0</v>
+      </c>
+      <c r="L154" s="1" t="str">
+        <v/>
+      </c>
+      <c r="M154" s="1">
+        <v>0</v>
+      </c>
+      <c r="N154" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O154" s="1">
+        <v>877500</v>
+      </c>
+      <c r="P154" s="1" t="str">
+        <v/>
+      </c>
+      <c r="Q154" s="1">
+        <v>877500</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155" s="1" t="str">
+        <v>0803229</v>
+      </c>
+      <c r="C155" s="1" t="str">
+        <v>웨이크업(wakup)</v>
+      </c>
+      <c r="D155" s="1" t="str">
+        <v>문구</v>
+      </c>
+      <c r="E155" s="1" t="str">
+        <v>IC0322900</v>
+      </c>
+      <c r="F155" s="1" t="str">
+        <v>웨이크업(wakup) 일반</v>
+      </c>
+      <c r="G155" s="1">
+        <v>0</v>
+      </c>
+      <c r="H155" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I155" s="1">
+        <v>0</v>
+      </c>
+      <c r="J155" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K155" s="1">
+        <v>0</v>
+      </c>
+      <c r="L155" s="1" t="str">
+        <v/>
+      </c>
+      <c r="M155" s="1">
+        <v>0</v>
+      </c>
+      <c r="N155" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O155" s="1">
+        <v>227600</v>
+      </c>
+      <c r="P155" s="1" t="str">
+        <v/>
+      </c>
+      <c r="Q155" s="1">
+        <v>227600</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156" s="1" t="str">
+        <v>0803288</v>
+      </c>
+      <c r="C156" s="1" t="str">
+        <v>명성코리아</v>
+      </c>
+      <c r="D156" s="1" t="str">
+        <v>문구</v>
+      </c>
+      <c r="E156" s="1" t="str">
+        <v>IC0328800</v>
+      </c>
+      <c r="F156" s="1" t="str">
+        <v>명성코리아 일반</v>
+      </c>
+      <c r="G156" s="1">
+        <v>0</v>
+      </c>
+      <c r="H156" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I156" s="1">
+        <v>0</v>
+      </c>
+      <c r="J156" s="1" t="str">
+        <v/>
+      </c>
+      <c r="K156" s="1">
+        <v>0</v>
+      </c>
+      <c r="L156" s="1" t="str">
+        <v/>
+      </c>
+      <c r="M156" s="1">
+        <v>0</v>
+      </c>
+      <c r="N156" s="1" t="str">
+        <v/>
+      </c>
+      <c r="O156" s="1">
+        <v>166950</v>
+      </c>
+      <c r="P156" s="1" t="str">
+        <v/>
+      </c>
+      <c r="Q156" s="1">
+        <v>166950</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q151"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q156"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -11936,18 +12297,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J151"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -16791,18 +17140,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J151"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -21646,18 +21983,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J151"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -26501,18 +26826,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J151"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -31355,19 +31668,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J151"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:J156"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -31406,31 +31707,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="str">
-        <v>0803080</v>
+        <v>0803176</v>
       </c>
       <c r="C2" s="1" t="str">
-        <v>위드에버상사</v>
+        <v>라이브워크</v>
       </c>
       <c r="D2" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E2" s="1" t="str">
-        <v>IC0308000</v>
+        <v>IC0317600</v>
       </c>
       <c r="F2" s="1" t="str">
-        <v>위드에버상사 일반</v>
+        <v>라이브워크 일반</v>
       </c>
       <c r="G2" s="1">
-        <v>1300000</v>
+        <v>2223710</v>
       </c>
       <c r="H2" s="1" t="str">
         <v/>
       </c>
       <c r="I2" s="1">
-        <v>1300000</v>
+        <v>2223710</v>
       </c>
       <c r="J2" s="1">
-        <v>2.8653</v>
+        <v>4.4213</v>
       </c>
     </row>
     <row r="3">
@@ -31438,31 +31739,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="str">
-        <v>0811513</v>
+        <v>0817560</v>
       </c>
       <c r="C3" s="1" t="str">
-        <v>캘리엠</v>
+        <v>도나앤데코</v>
       </c>
       <c r="D3" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E3" s="1" t="str">
-        <v>IC0151300</v>
+        <v>IC0756000</v>
       </c>
       <c r="F3" s="1" t="str">
-        <v>캘리엠 일반</v>
+        <v>도나앤데코 일반</v>
       </c>
       <c r="G3" s="1">
-        <v>1080000</v>
+        <v>1429400</v>
       </c>
       <c r="H3" s="1" t="str">
         <v/>
       </c>
       <c r="I3" s="1">
-        <v>1080000</v>
+        <v>1429400</v>
       </c>
       <c r="J3" s="1">
-        <v>2.3804</v>
+        <v>2.842</v>
       </c>
     </row>
     <row r="4">
@@ -31470,31 +31771,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="str">
-        <v>0817625</v>
+        <v>0803080</v>
       </c>
       <c r="C4" s="1" t="str">
-        <v>대인커머스</v>
+        <v>위드에버상사</v>
       </c>
       <c r="D4" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E4" s="1" t="str">
-        <v>IC0762500</v>
+        <v>IC0308000</v>
       </c>
       <c r="F4" s="1" t="str">
-        <v>대인커머스 일반</v>
+        <v>위드에버상사 일반</v>
       </c>
       <c r="G4" s="1">
-        <v>1040000</v>
+        <v>1300000</v>
       </c>
       <c r="H4" s="1" t="str">
         <v/>
       </c>
       <c r="I4" s="1">
-        <v>1040000</v>
+        <v>1300000</v>
       </c>
       <c r="J4" s="1">
-        <v>2.2923</v>
+        <v>2.5847</v>
       </c>
     </row>
     <row r="5">
@@ -31502,31 +31803,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="str">
-        <v>0818036</v>
+        <v>0811513</v>
       </c>
       <c r="C5" s="1" t="str">
-        <v>페펜스튜디오</v>
+        <v>캘리엠</v>
       </c>
       <c r="D5" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E5" s="1" t="str">
-        <v>IC0803600</v>
+        <v>IC0151300</v>
       </c>
       <c r="F5" s="1" t="str">
-        <v>페펜스튜디오 일반</v>
+        <v>캘리엠 일반</v>
       </c>
       <c r="G5" s="1">
-        <v>990000</v>
+        <v>1080000</v>
       </c>
       <c r="H5" s="1" t="str">
         <v/>
       </c>
       <c r="I5" s="1">
-        <v>990000</v>
+        <v>1080000</v>
       </c>
       <c r="J5" s="1">
-        <v>2.1821</v>
+        <v>2.1473</v>
       </c>
     </row>
     <row r="6">
@@ -31534,31 +31835,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="str">
-        <v>0810456</v>
+        <v>0817625</v>
       </c>
       <c r="C6" s="1" t="str">
-        <v>디앤에프조이필</v>
+        <v>대인커머스</v>
       </c>
       <c r="D6" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E6" s="1" t="str">
-        <v>IC0045600</v>
+        <v>IC0762500</v>
       </c>
       <c r="F6" s="1" t="str">
-        <v>디앤에프조이필 일반</v>
+        <v>대인커머스 일반</v>
       </c>
       <c r="G6" s="1">
-        <v>990000</v>
+        <v>1040000</v>
       </c>
       <c r="H6" s="1" t="str">
         <v/>
       </c>
       <c r="I6" s="1">
-        <v>990000</v>
+        <v>1040000</v>
       </c>
       <c r="J6" s="1">
-        <v>2.1821</v>
+        <v>2.0678</v>
       </c>
     </row>
     <row r="7">
@@ -31566,31 +31867,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="str">
-        <v>0803289</v>
+        <v>0818036</v>
       </c>
       <c r="C7" s="1" t="str">
-        <v>솜씨스템프</v>
+        <v>페펜스튜디오</v>
       </c>
       <c r="D7" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E7" s="1" t="str">
-        <v>IC0328900</v>
+        <v>IC0803600</v>
       </c>
       <c r="F7" s="1" t="str">
-        <v>솜씨스템프 일반</v>
+        <v>페펜스튜디오 일반</v>
       </c>
       <c r="G7" s="1">
-        <v>950000</v>
+        <v>990000</v>
       </c>
       <c r="H7" s="1" t="str">
         <v/>
       </c>
       <c r="I7" s="1">
-        <v>950000</v>
+        <v>990000</v>
       </c>
       <c r="J7" s="1">
-        <v>2.0939</v>
+        <v>1.9684</v>
       </c>
     </row>
     <row r="8">
@@ -31598,31 +31899,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="str">
-        <v>0803267</v>
+        <v>0810456</v>
       </c>
       <c r="C8" s="1" t="str">
-        <v>플레플레</v>
+        <v>디앤에프조이필</v>
       </c>
       <c r="D8" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E8" s="1" t="str">
-        <v>IC0326700</v>
+        <v>IC0045600</v>
       </c>
       <c r="F8" s="1" t="str">
-        <v>플레플레 일반</v>
+        <v>디앤에프조이필 일반</v>
       </c>
       <c r="G8" s="1">
-        <v>950000</v>
+        <v>990000</v>
       </c>
       <c r="H8" s="1" t="str">
         <v/>
       </c>
       <c r="I8" s="1">
-        <v>950000</v>
+        <v>990000</v>
       </c>
       <c r="J8" s="1">
-        <v>2.0939</v>
+        <v>1.9684</v>
       </c>
     </row>
     <row r="9">
@@ -31630,19 +31931,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="str">
-        <v>0803255</v>
+        <v>0803289</v>
       </c>
       <c r="C9" s="1" t="str">
-        <v>모닝글로리</v>
+        <v>솜씨스템프</v>
       </c>
       <c r="D9" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E9" s="1" t="str">
-        <v>IC0325500</v>
+        <v>IC0328900</v>
       </c>
       <c r="F9" s="1" t="str">
-        <v>모닝글로리 일반</v>
+        <v>솜씨스템프 일반</v>
       </c>
       <c r="G9" s="1">
         <v>950000</v>
@@ -31654,7 +31955,7 @@
         <v>950000</v>
       </c>
       <c r="J9" s="1">
-        <v>2.0939</v>
+        <v>1.8888</v>
       </c>
     </row>
     <row r="10">
@@ -31662,31 +31963,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="str">
-        <v>0900224</v>
+        <v>0803267</v>
       </c>
       <c r="C10" s="1" t="str">
-        <v>LIHIT LAB.,INC</v>
+        <v>플레플레</v>
       </c>
       <c r="D10" s="1" t="str">
-        <v>해외문구</v>
+        <v>문구</v>
       </c>
       <c r="E10" s="1" t="str">
-        <v>IC0022400</v>
+        <v>IC0326700</v>
       </c>
       <c r="F10" s="1" t="str">
-        <v>LIHIT LAB.,INC 일반</v>
+        <v>플레플레 일반</v>
       </c>
       <c r="G10" s="1">
-        <v>920000</v>
+        <v>950000</v>
       </c>
       <c r="H10" s="1" t="str">
         <v/>
       </c>
       <c r="I10" s="1">
-        <v>920000</v>
+        <v>950000</v>
       </c>
       <c r="J10" s="1">
-        <v>2.0278</v>
+        <v>1.8888</v>
       </c>
     </row>
     <row r="11">
@@ -31694,31 +31995,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="str">
-        <v>0900216</v>
+        <v>0803255</v>
       </c>
       <c r="C11" s="1" t="str">
-        <v>LEUCHTTURM</v>
+        <v>모닝글로리</v>
       </c>
       <c r="D11" s="1" t="str">
-        <v>해외문구</v>
+        <v>문구</v>
       </c>
       <c r="E11" s="1" t="str">
-        <v>IC0021600</v>
+        <v>IC0325500</v>
       </c>
       <c r="F11" s="1" t="str">
-        <v>LEUCHTTURM 일반</v>
+        <v>모닝글로리 일반</v>
       </c>
       <c r="G11" s="1">
-        <v>910000</v>
+        <v>950000</v>
       </c>
       <c r="H11" s="1" t="str">
         <v/>
       </c>
       <c r="I11" s="1">
-        <v>910000</v>
+        <v>950000</v>
       </c>
       <c r="J11" s="1">
-        <v>2.0057</v>
+        <v>1.8888</v>
       </c>
     </row>
     <row r="12">
@@ -31726,31 +32027,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="str">
-        <v>0816903</v>
+        <v>0900224</v>
       </c>
       <c r="C12" s="1" t="str">
-        <v>더시호</v>
+        <v>LIHIT LAB.,INC</v>
       </c>
       <c r="D12" s="1" t="str">
-        <v>문구</v>
+        <v>해외문구</v>
       </c>
       <c r="E12" s="1" t="str">
-        <v>IC0690300</v>
+        <v>IC0022400</v>
       </c>
       <c r="F12" s="1" t="str">
-        <v>더시호 일반</v>
+        <v>LIHIT LAB.,INC 일반</v>
       </c>
       <c r="G12" s="1">
-        <v>890000</v>
+        <v>920000</v>
       </c>
       <c r="H12" s="1" t="str">
         <v/>
       </c>
       <c r="I12" s="1">
-        <v>890000</v>
+        <v>920000</v>
       </c>
       <c r="J12" s="1">
-        <v>1.9616</v>
+        <v>1.8292</v>
       </c>
     </row>
     <row r="13">
@@ -31758,31 +32059,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="str">
-        <v>0803186</v>
+        <v>0900216</v>
       </c>
       <c r="C13" s="1" t="str">
-        <v>아이코닉</v>
+        <v>LEUCHTTURM</v>
       </c>
       <c r="D13" s="1" t="str">
-        <v>문구</v>
+        <v>해외문구</v>
       </c>
       <c r="E13" s="1" t="str">
-        <v>IC0318600</v>
+        <v>IC0021600</v>
       </c>
       <c r="F13" s="1" t="str">
-        <v>아이코닉 일반</v>
+        <v>LEUCHTTURM 일반</v>
       </c>
       <c r="G13" s="1">
-        <v>870000</v>
+        <v>910000</v>
       </c>
       <c r="H13" s="1" t="str">
         <v/>
       </c>
       <c r="I13" s="1">
-        <v>870000</v>
+        <v>910000</v>
       </c>
       <c r="J13" s="1">
-        <v>1.9176</v>
+        <v>1.8093</v>
       </c>
     </row>
     <row r="14">
@@ -31790,31 +32091,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="str">
-        <v>0803187</v>
+        <v>0816903</v>
       </c>
       <c r="C14" s="1" t="str">
-        <v>칠삼이일디자인</v>
+        <v>더시호</v>
       </c>
       <c r="D14" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E14" s="1" t="str">
-        <v>IC0318700</v>
+        <v>IC0690300</v>
       </c>
       <c r="F14" s="1" t="str">
-        <v>칠삼이일디자인 일반</v>
+        <v>더시호 일반</v>
       </c>
       <c r="G14" s="1">
-        <v>870000</v>
+        <v>890000</v>
       </c>
       <c r="H14" s="1" t="str">
         <v/>
       </c>
       <c r="I14" s="1">
-        <v>870000</v>
+        <v>890000</v>
       </c>
       <c r="J14" s="1">
-        <v>1.9176</v>
+        <v>1.7696</v>
       </c>
     </row>
     <row r="15">
@@ -31822,31 +32123,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="str">
-        <v>0803159</v>
+        <v>0806606</v>
       </c>
       <c r="C15" s="1" t="str">
-        <v>안테나샵</v>
+        <v>디자인랩(레더랩)</v>
       </c>
       <c r="D15" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E15" s="1" t="str">
-        <v>IC0315900</v>
+        <v>IC0660600</v>
       </c>
       <c r="F15" s="1" t="str">
-        <v>안테나샵 일반</v>
+        <v>디자인랩(레더랩) 일반</v>
       </c>
       <c r="G15" s="1">
-        <v>860000</v>
+        <v>877500</v>
       </c>
       <c r="H15" s="1" t="str">
         <v/>
       </c>
       <c r="I15" s="1">
-        <v>860000</v>
+        <v>877500</v>
       </c>
       <c r="J15" s="1">
-        <v>1.8955</v>
+        <v>1.7447</v>
       </c>
     </row>
     <row r="16">
@@ -31854,31 +32155,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="str">
-        <v>0803144</v>
+        <v>0803186</v>
       </c>
       <c r="C16" s="1" t="str">
-        <v>씨케이세일즈</v>
+        <v>아이코닉</v>
       </c>
       <c r="D16" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E16" s="1" t="str">
-        <v>IC0314400</v>
+        <v>IC0318600</v>
       </c>
       <c r="F16" s="1" t="str">
-        <v>씨케이세일즈 일반</v>
+        <v>아이코닉 일반</v>
       </c>
       <c r="G16" s="1">
-        <v>860000</v>
+        <v>870000</v>
       </c>
       <c r="H16" s="1" t="str">
         <v/>
       </c>
       <c r="I16" s="1">
-        <v>860000</v>
+        <v>870000</v>
       </c>
       <c r="J16" s="1">
-        <v>1.8955</v>
+        <v>1.7298</v>
       </c>
     </row>
     <row r="17">
@@ -31886,31 +32187,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="str">
-        <v>0803158</v>
+        <v>0803187</v>
       </c>
       <c r="C17" s="1" t="str">
-        <v>바이풀디자인</v>
+        <v>칠삼이일디자인</v>
       </c>
       <c r="D17" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E17" s="1" t="str">
-        <v>IC0315800</v>
+        <v>IC0318700</v>
       </c>
       <c r="F17" s="1" t="str">
-        <v>바이풀디자인 일반</v>
+        <v>칠삼이일디자인 일반</v>
       </c>
       <c r="G17" s="1">
-        <v>860000</v>
+        <v>870000</v>
       </c>
       <c r="H17" s="1" t="str">
         <v/>
       </c>
       <c r="I17" s="1">
-        <v>860000</v>
+        <v>870000</v>
       </c>
       <c r="J17" s="1">
-        <v>1.8955</v>
+        <v>1.7298</v>
       </c>
     </row>
     <row r="18">
@@ -31918,31 +32219,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="str">
-        <v>0803124</v>
+        <v>0803159</v>
       </c>
       <c r="C18" s="1" t="str">
-        <v>아톰상사(특정매입)</v>
+        <v>안테나샵</v>
       </c>
       <c r="D18" s="1" t="str">
-        <v>특정매입</v>
+        <v>문구</v>
       </c>
       <c r="E18" s="1" t="str">
-        <v>IC0312400</v>
+        <v>IC0315900</v>
       </c>
       <c r="F18" s="1" t="str">
-        <v>아톰상사(특정매입) 일반</v>
+        <v>안테나샵 일반</v>
       </c>
       <c r="G18" s="1">
-        <v>850000</v>
+        <v>860000</v>
       </c>
       <c r="H18" s="1" t="str">
         <v/>
       </c>
       <c r="I18" s="1">
-        <v>850000</v>
+        <v>860000</v>
       </c>
       <c r="J18" s="1">
-        <v>1.8735</v>
+        <v>1.7099</v>
       </c>
     </row>
     <row r="19">
@@ -31950,31 +32251,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="str">
-        <v>0811795</v>
+        <v>0803144</v>
       </c>
       <c r="C19" s="1" t="str">
-        <v>베르제마넷</v>
+        <v>씨케이세일즈</v>
       </c>
       <c r="D19" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E19" s="1" t="str">
-        <v>IC0179500</v>
+        <v>IC0314400</v>
       </c>
       <c r="F19" s="1" t="str">
-        <v>베르제마넷 일반</v>
+        <v>씨케이세일즈 일반</v>
       </c>
       <c r="G19" s="1">
-        <v>850000</v>
+        <v>860000</v>
       </c>
       <c r="H19" s="1" t="str">
         <v/>
       </c>
       <c r="I19" s="1">
-        <v>850000</v>
+        <v>860000</v>
       </c>
       <c r="J19" s="1">
-        <v>1.8735</v>
+        <v>1.7099</v>
       </c>
     </row>
     <row r="20">
@@ -31982,31 +32283,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="str">
-        <v>0803222</v>
+        <v>0803158</v>
       </c>
       <c r="C20" s="1" t="str">
-        <v>아르디움</v>
+        <v>바이풀디자인</v>
       </c>
       <c r="D20" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E20" s="1" t="str">
-        <v>IC0322200</v>
+        <v>IC0315800</v>
       </c>
       <c r="F20" s="1" t="str">
-        <v>아르디움 일반</v>
+        <v>바이풀디자인 일반</v>
       </c>
       <c r="G20" s="1">
-        <v>940000</v>
-      </c>
-      <c r="H20" s="1">
-        <v>140000</v>
+        <v>860000</v>
+      </c>
+      <c r="H20" s="1" t="str">
+        <v/>
       </c>
       <c r="I20" s="1">
-        <v>800000</v>
+        <v>860000</v>
       </c>
       <c r="J20" s="1">
-        <v>1.7633</v>
+        <v>1.7099</v>
       </c>
     </row>
     <row r="21">
@@ -32014,31 +32315,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="str">
-        <v>0900252</v>
+        <v>0803124</v>
       </c>
       <c r="C21" s="1" t="str">
-        <v>HIGHTIDE CO.,LTD</v>
+        <v>아톰상사(특정매입)</v>
       </c>
       <c r="D21" s="1" t="str">
-        <v>해외문구</v>
+        <v>특정매입</v>
       </c>
       <c r="E21" s="1" t="str">
-        <v>IC0025200</v>
+        <v>IC0312400</v>
       </c>
       <c r="F21" s="1" t="str">
-        <v>HIGHTIDE CO.,LTD 일반</v>
+        <v>아톰상사(특정매입) 일반</v>
       </c>
       <c r="G21" s="1">
-        <v>920000</v>
-      </c>
-      <c r="H21" s="1">
-        <v>140000</v>
+        <v>850000</v>
+      </c>
+      <c r="H21" s="1" t="str">
+        <v/>
       </c>
       <c r="I21" s="1">
-        <v>780000</v>
+        <v>850000</v>
       </c>
       <c r="J21" s="1">
-        <v>1.7192</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="22">
@@ -32046,31 +32347,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="str">
-        <v>0816796</v>
+        <v>0811795</v>
       </c>
       <c r="C22" s="1" t="str">
-        <v>마이누</v>
+        <v>베르제마넷</v>
       </c>
       <c r="D22" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E22" s="1" t="str">
-        <v>IC0679600</v>
+        <v>IC0179500</v>
       </c>
       <c r="F22" s="1" t="str">
-        <v>마이누 일반</v>
+        <v>베르제마넷 일반</v>
       </c>
       <c r="G22" s="1">
-        <v>750000</v>
+        <v>850000</v>
       </c>
       <c r="H22" s="1" t="str">
         <v/>
       </c>
       <c r="I22" s="1">
-        <v>750000</v>
+        <v>850000</v>
       </c>
       <c r="J22" s="1">
-        <v>1.6531</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="23">
@@ -32078,31 +32379,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="str">
-        <v>0810588</v>
+        <v>0803222</v>
       </c>
       <c r="C23" s="1" t="str">
-        <v>케이디코퍼레이션</v>
+        <v>아르디움</v>
       </c>
       <c r="D23" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E23" s="1" t="str">
-        <v>IC0058800</v>
+        <v>IC0322200</v>
       </c>
       <c r="F23" s="1" t="str">
-        <v>케이디코퍼레이션 일반</v>
+        <v>아르디움 일반</v>
       </c>
       <c r="G23" s="1">
-        <v>680000</v>
-      </c>
-      <c r="H23" s="1" t="str">
-        <v/>
+        <v>940000</v>
+      </c>
+      <c r="H23" s="1">
+        <v>140000</v>
       </c>
       <c r="I23" s="1">
-        <v>680000</v>
+        <v>800000</v>
       </c>
       <c r="J23" s="1">
-        <v>1.4988</v>
+        <v>1.5906</v>
       </c>
     </row>
     <row r="24">
@@ -32110,31 +32411,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="str">
-        <v>0803289</v>
+        <v>0900252</v>
       </c>
       <c r="C24" s="1" t="str">
-        <v>솜씨스템프</v>
+        <v>HIGHTIDE CO.,LTD</v>
       </c>
       <c r="D24" s="1" t="str">
-        <v>문구</v>
+        <v>해외문구</v>
       </c>
       <c r="E24" s="1" t="str">
-        <v>IC0328901</v>
+        <v>IC0025200</v>
       </c>
       <c r="F24" s="1" t="str">
-        <v>솜씨스템프 증정</v>
+        <v>HIGHTIDE CO.,LTD 일반</v>
       </c>
       <c r="G24" s="1">
-        <v>640000</v>
-      </c>
-      <c r="H24" s="1" t="str">
-        <v/>
+        <v>920000</v>
+      </c>
+      <c r="H24" s="1">
+        <v>140000</v>
       </c>
       <c r="I24" s="1">
-        <v>640000</v>
+        <v>780000</v>
       </c>
       <c r="J24" s="1">
-        <v>1.4106</v>
+        <v>1.5508</v>
       </c>
     </row>
     <row r="25">
@@ -32142,31 +32443,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="str">
-        <v>0817604</v>
+        <v>0816796</v>
       </c>
       <c r="C25" s="1" t="str">
-        <v>비온뒤</v>
+        <v>마이누</v>
       </c>
       <c r="D25" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E25" s="1" t="str">
-        <v>IC0760400</v>
+        <v>IC0679600</v>
       </c>
       <c r="F25" s="1" t="str">
-        <v>비온뒤 일반</v>
+        <v>마이누 일반</v>
       </c>
       <c r="G25" s="1">
-        <v>620000</v>
+        <v>750000</v>
       </c>
       <c r="H25" s="1" t="str">
         <v/>
       </c>
       <c r="I25" s="1">
-        <v>620000</v>
+        <v>750000</v>
       </c>
       <c r="J25" s="1">
-        <v>1.3665</v>
+        <v>1.4912</v>
       </c>
     </row>
     <row r="26">
@@ -32174,31 +32475,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="str">
-        <v>0818620</v>
+        <v>0810588</v>
       </c>
       <c r="C26" s="1" t="str">
-        <v>더토브</v>
+        <v>케이디코퍼레이션</v>
       </c>
       <c r="D26" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E26" s="1" t="str">
-        <v>IC0862000</v>
+        <v>IC0058800</v>
       </c>
       <c r="F26" s="1" t="str">
-        <v>더토브 일반</v>
+        <v>케이디코퍼레이션 일반</v>
       </c>
       <c r="G26" s="1">
-        <v>610000</v>
+        <v>680000</v>
       </c>
       <c r="H26" s="1" t="str">
         <v/>
       </c>
       <c r="I26" s="1">
-        <v>610000</v>
+        <v>680000</v>
       </c>
       <c r="J26" s="1">
-        <v>1.3445</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="27">
@@ -32206,31 +32507,31 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="str">
-        <v>0803144</v>
+        <v>0803289</v>
       </c>
       <c r="C27" s="1" t="str">
-        <v>씨케이세일즈</v>
+        <v>솜씨스템프</v>
       </c>
       <c r="D27" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E27" s="1" t="str">
-        <v>IC0314401</v>
+        <v>IC0328901</v>
       </c>
       <c r="F27" s="1" t="str">
-        <v>씨케이세일즈 특가</v>
+        <v>솜씨스템프 증정</v>
       </c>
       <c r="G27" s="1">
-        <v>570000</v>
+        <v>640000</v>
       </c>
       <c r="H27" s="1" t="str">
         <v/>
       </c>
       <c r="I27" s="1">
-        <v>570000</v>
+        <v>640000</v>
       </c>
       <c r="J27" s="1">
-        <v>1.2563</v>
+        <v>1.2725</v>
       </c>
     </row>
     <row r="28">
@@ -32238,31 +32539,31 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="str">
-        <v>0803158</v>
+        <v>0817604</v>
       </c>
       <c r="C28" s="1" t="str">
-        <v>바이풀디자인</v>
+        <v>비온뒤</v>
       </c>
       <c r="D28" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E28" s="1" t="str">
-        <v>IC0315801</v>
+        <v>IC0760400</v>
       </c>
       <c r="F28" s="1" t="str">
-        <v>바이풀디자인 정품</v>
+        <v>비온뒤 일반</v>
       </c>
       <c r="G28" s="1">
-        <v>570000</v>
+        <v>620000</v>
       </c>
       <c r="H28" s="1" t="str">
         <v/>
       </c>
       <c r="I28" s="1">
-        <v>570000</v>
+        <v>620000</v>
       </c>
       <c r="J28" s="1">
-        <v>1.2563</v>
+        <v>1.2327</v>
       </c>
     </row>
     <row r="29">
@@ -32270,31 +32571,31 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="str">
-        <v>0816555</v>
+        <v>0818620</v>
       </c>
       <c r="C29" s="1" t="str">
-        <v>냐냐온 스튜디오</v>
+        <v>더토브</v>
       </c>
       <c r="D29" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E29" s="1" t="str">
-        <v>IC0655500</v>
+        <v>IC0862000</v>
       </c>
       <c r="F29" s="1" t="str">
-        <v>냐냐온 스튜디오 일반</v>
+        <v>더토브 일반</v>
       </c>
       <c r="G29" s="1">
-        <v>560000</v>
+        <v>610000</v>
       </c>
       <c r="H29" s="1" t="str">
         <v/>
       </c>
       <c r="I29" s="1">
-        <v>560000</v>
+        <v>610000</v>
       </c>
       <c r="J29" s="1">
-        <v>1.2343</v>
+        <v>1.2128</v>
       </c>
     </row>
     <row r="30">
@@ -32302,31 +32603,31 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="str">
-        <v>0816525</v>
+        <v>0803144</v>
       </c>
       <c r="C30" s="1" t="str">
-        <v>루카랩컴퍼니</v>
+        <v>씨케이세일즈</v>
       </c>
       <c r="D30" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E30" s="1" t="str">
-        <v>IC0652500</v>
+        <v>IC0314401</v>
       </c>
       <c r="F30" s="1" t="str">
-        <v>루카랩컴퍼니 일반</v>
+        <v>씨케이세일즈 특가</v>
       </c>
       <c r="G30" s="1">
-        <v>560000</v>
+        <v>570000</v>
       </c>
       <c r="H30" s="1" t="str">
         <v/>
       </c>
       <c r="I30" s="1">
-        <v>560000</v>
+        <v>570000</v>
       </c>
       <c r="J30" s="1">
-        <v>1.2343</v>
+        <v>1.1333</v>
       </c>
     </row>
     <row r="31">
@@ -32334,31 +32635,31 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="str">
-        <v>0803825</v>
+        <v>0803158</v>
       </c>
       <c r="C31" s="1" t="str">
-        <v>정인통상</v>
+        <v>바이풀디자인</v>
       </c>
       <c r="D31" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E31" s="1" t="str">
-        <v>IC0382500</v>
+        <v>IC0315801</v>
       </c>
       <c r="F31" s="1" t="str">
-        <v>정인통상 일반</v>
+        <v>바이풀디자인 정품</v>
       </c>
       <c r="G31" s="1">
-        <v>560000</v>
+        <v>570000</v>
       </c>
       <c r="H31" s="1" t="str">
         <v/>
       </c>
       <c r="I31" s="1">
-        <v>560000</v>
+        <v>570000</v>
       </c>
       <c r="J31" s="1">
-        <v>1.2343</v>
+        <v>1.1333</v>
       </c>
     </row>
     <row r="32">
@@ -32366,19 +32667,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="str">
-        <v>0803833</v>
+        <v>0816555</v>
       </c>
       <c r="C32" s="1" t="str">
-        <v>모나미(특정매입)</v>
+        <v>냐냐온 스튜디오</v>
       </c>
       <c r="D32" s="1" t="str">
-        <v>특정매입</v>
+        <v>문구</v>
       </c>
       <c r="E32" s="1" t="str">
-        <v>IC0383300</v>
+        <v>IC0655500</v>
       </c>
       <c r="F32" s="1" t="str">
-        <v>모나미(특정매입) 일반</v>
+        <v>냐냐온 스튜디오 일반</v>
       </c>
       <c r="G32" s="1">
         <v>560000</v>
@@ -32390,7 +32691,7 @@
         <v>560000</v>
       </c>
       <c r="J32" s="1">
-        <v>1.2343</v>
+        <v>1.1134</v>
       </c>
     </row>
     <row r="33">
@@ -32398,31 +32699,31 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="str">
-        <v>0817528</v>
+        <v>0816525</v>
       </c>
       <c r="C33" s="1" t="str">
-        <v>누크코퍼레이션</v>
+        <v>루카랩컴퍼니</v>
       </c>
       <c r="D33" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E33" s="1" t="str">
-        <v>IC0752800</v>
+        <v>IC0652500</v>
       </c>
       <c r="F33" s="1" t="str">
-        <v>누크코퍼레이션 일반</v>
+        <v>루카랩컴퍼니 일반</v>
       </c>
       <c r="G33" s="1">
-        <v>540000</v>
+        <v>560000</v>
       </c>
       <c r="H33" s="1" t="str">
         <v/>
       </c>
       <c r="I33" s="1">
-        <v>540000</v>
+        <v>560000</v>
       </c>
       <c r="J33" s="1">
-        <v>1.1902</v>
+        <v>1.1134</v>
       </c>
     </row>
     <row r="34">
@@ -32430,31 +32731,31 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="str">
-        <v>0803791</v>
+        <v>0803825</v>
       </c>
       <c r="C34" s="1" t="str">
-        <v>공장</v>
+        <v>정인통상</v>
       </c>
       <c r="D34" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E34" s="1" t="str">
-        <v>IC0379100</v>
+        <v>IC0382500</v>
       </c>
       <c r="F34" s="1" t="str">
-        <v>공장 일반</v>
+        <v>정인통상 일반</v>
       </c>
       <c r="G34" s="1">
-        <v>490000</v>
+        <v>560000</v>
       </c>
       <c r="H34" s="1" t="str">
         <v/>
       </c>
       <c r="I34" s="1">
-        <v>490000</v>
+        <v>560000</v>
       </c>
       <c r="J34" s="1">
-        <v>1.08</v>
+        <v>1.1134</v>
       </c>
     </row>
     <row r="35">
@@ -32462,31 +32763,31 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="str">
-        <v>0803503</v>
+        <v>0803833</v>
       </c>
       <c r="C35" s="1" t="str">
-        <v>로마네</v>
+        <v>모나미(특정매입)</v>
       </c>
       <c r="D35" s="1" t="str">
-        <v>문구</v>
+        <v>특정매입</v>
       </c>
       <c r="E35" s="1" t="str">
-        <v>IC0350300</v>
+        <v>IC0383300</v>
       </c>
       <c r="F35" s="1" t="str">
-        <v>로마네 일반</v>
+        <v>모나미(특정매입) 일반</v>
       </c>
       <c r="G35" s="1">
-        <v>480000</v>
+        <v>560000</v>
       </c>
       <c r="H35" s="1" t="str">
         <v/>
       </c>
       <c r="I35" s="1">
-        <v>480000</v>
+        <v>560000</v>
       </c>
       <c r="J35" s="1">
-        <v>1.058</v>
+        <v>1.1134</v>
       </c>
     </row>
     <row r="36">
@@ -32494,31 +32795,31 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="str">
-        <v>0803741</v>
+        <v>0817528</v>
       </c>
       <c r="C36" s="1" t="str">
-        <v>BST</v>
+        <v>누크코퍼레이션</v>
       </c>
       <c r="D36" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E36" s="1" t="str">
-        <v>IC0374100</v>
+        <v>IC0752800</v>
       </c>
       <c r="F36" s="1" t="str">
-        <v>BST 일반</v>
+        <v>누크코퍼레이션 일반</v>
       </c>
       <c r="G36" s="1">
-        <v>470000</v>
+        <v>540000</v>
       </c>
       <c r="H36" s="1" t="str">
         <v/>
       </c>
       <c r="I36" s="1">
-        <v>470000</v>
+        <v>540000</v>
       </c>
       <c r="J36" s="1">
-        <v>1.0359</v>
+        <v>1.0737</v>
       </c>
     </row>
     <row r="37">
@@ -32526,31 +32827,31 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="str">
-        <v>0810588</v>
+        <v>0803791</v>
       </c>
       <c r="C37" s="1" t="str">
-        <v>케이디코퍼레이션</v>
+        <v>공장</v>
       </c>
       <c r="D37" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E37" s="1" t="str">
-        <v>IC0058801</v>
+        <v>IC0379100</v>
       </c>
       <c r="F37" s="1" t="str">
-        <v>케이디코퍼레이션 문구행사</v>
+        <v>공장 일반</v>
       </c>
       <c r="G37" s="1">
-        <v>460000</v>
+        <v>490000</v>
       </c>
       <c r="H37" s="1" t="str">
         <v/>
       </c>
       <c r="I37" s="1">
-        <v>460000</v>
+        <v>490000</v>
       </c>
       <c r="J37" s="1">
-        <v>1.0139</v>
+        <v>0.9742</v>
       </c>
     </row>
     <row r="38">
@@ -32558,31 +32859,31 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="str">
-        <v>0806798</v>
+        <v>0803503</v>
       </c>
       <c r="C38" s="1" t="str">
-        <v>이가라인유통</v>
+        <v>로마네</v>
       </c>
       <c r="D38" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E38" s="1" t="str">
-        <v>IC0679800</v>
+        <v>IC0350300</v>
       </c>
       <c r="F38" s="1" t="str">
-        <v>이가라인유통 일반</v>
+        <v>로마네 일반</v>
       </c>
       <c r="G38" s="1">
-        <v>430000</v>
+        <v>480000</v>
       </c>
       <c r="H38" s="1" t="str">
         <v/>
       </c>
       <c r="I38" s="1">
-        <v>430000</v>
+        <v>480000</v>
       </c>
       <c r="J38" s="1">
-        <v>0.9478</v>
+        <v>0.9544</v>
       </c>
     </row>
     <row r="39">
@@ -32590,31 +32891,31 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="str">
-        <v>0818620</v>
+        <v>0803741</v>
       </c>
       <c r="C39" s="1" t="str">
-        <v>더토브</v>
+        <v>BST</v>
       </c>
       <c r="D39" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E39" s="1" t="str">
-        <v>IC0862001</v>
+        <v>IC0374100</v>
       </c>
       <c r="F39" s="1" t="str">
-        <v>더토브 대표상품</v>
+        <v>BST 일반</v>
       </c>
       <c r="G39" s="1">
-        <v>400000</v>
+        <v>470000</v>
       </c>
       <c r="H39" s="1" t="str">
         <v/>
       </c>
       <c r="I39" s="1">
-        <v>400000</v>
+        <v>470000</v>
       </c>
       <c r="J39" s="1">
-        <v>0.8816</v>
+        <v>0.9345</v>
       </c>
     </row>
     <row r="40">
@@ -32622,31 +32923,31 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="str">
-        <v>0803690</v>
+        <v>0810588</v>
       </c>
       <c r="C40" s="1" t="str">
-        <v>인디고</v>
+        <v>케이디코퍼레이션</v>
       </c>
       <c r="D40" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E40" s="1" t="str">
-        <v>IC0369000</v>
+        <v>IC0058801</v>
       </c>
       <c r="F40" s="1" t="str">
-        <v>인디고 일반</v>
+        <v>케이디코퍼레이션 문구행사</v>
       </c>
       <c r="G40" s="1">
-        <v>400000</v>
+        <v>460000</v>
       </c>
       <c r="H40" s="1" t="str">
         <v/>
       </c>
       <c r="I40" s="1">
-        <v>400000</v>
+        <v>460000</v>
       </c>
       <c r="J40" s="1">
-        <v>0.8816</v>
+        <v>0.9146</v>
       </c>
     </row>
     <row r="41">
@@ -32654,31 +32955,31 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="str">
-        <v>0816555</v>
+        <v>0806798</v>
       </c>
       <c r="C41" s="1" t="str">
-        <v>냐냐온 스튜디오</v>
+        <v>이가라인유통</v>
       </c>
       <c r="D41" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E41" s="1" t="str">
-        <v>IC0655501</v>
+        <v>IC0679800</v>
       </c>
       <c r="F41" s="1" t="str">
-        <v>냐냐온 스튜디오 문구행사</v>
+        <v>이가라인유통 일반</v>
       </c>
       <c r="G41" s="1">
-        <v>380000</v>
+        <v>430000</v>
       </c>
       <c r="H41" s="1" t="str">
         <v/>
       </c>
       <c r="I41" s="1">
-        <v>380000</v>
+        <v>430000</v>
       </c>
       <c r="J41" s="1">
-        <v>0.8376</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="42">
@@ -32686,31 +32987,31 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="str">
-        <v>0803833</v>
+        <v>0818620</v>
       </c>
       <c r="C42" s="1" t="str">
-        <v>모나미(특정매입)</v>
+        <v>더토브</v>
       </c>
       <c r="D42" s="1" t="str">
-        <v>특정매입</v>
+        <v>문구</v>
       </c>
       <c r="E42" s="1" t="str">
-        <v>IC0383301</v>
+        <v>IC0862001</v>
       </c>
       <c r="F42" s="1" t="str">
-        <v>모나미(특정매입) 시즌특가</v>
+        <v>더토브 대표상품</v>
       </c>
       <c r="G42" s="1">
-        <v>370000</v>
+        <v>400000</v>
       </c>
       <c r="H42" s="1" t="str">
         <v/>
       </c>
       <c r="I42" s="1">
-        <v>370000</v>
+        <v>400000</v>
       </c>
       <c r="J42" s="1">
-        <v>0.8155</v>
+        <v>0.7953</v>
       </c>
     </row>
     <row r="43">
@@ -32718,31 +33019,31 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="str">
-        <v>0818036</v>
+        <v>0803690</v>
       </c>
       <c r="C43" s="1" t="str">
-        <v>페펜스튜디오</v>
+        <v>인디고</v>
       </c>
       <c r="D43" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E43" s="1" t="str">
-        <v>IC0803601</v>
+        <v>IC0369000</v>
       </c>
       <c r="F43" s="1" t="str">
-        <v>페펜스튜디오 특가</v>
+        <v>인디고 일반</v>
       </c>
       <c r="G43" s="1">
-        <v>330000</v>
+        <v>400000</v>
       </c>
       <c r="H43" s="1" t="str">
         <v/>
       </c>
       <c r="I43" s="1">
-        <v>330000</v>
+        <v>400000</v>
       </c>
       <c r="J43" s="1">
-        <v>0.7274</v>
+        <v>0.7953</v>
       </c>
     </row>
     <row r="44">
@@ -32750,31 +33051,31 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="str">
-        <v>0818036</v>
+        <v>0816555</v>
       </c>
       <c r="C44" s="1" t="str">
-        <v>페펜스튜디오</v>
+        <v>냐냐온 스튜디오</v>
       </c>
       <c r="D44" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E44" s="1" t="str">
-        <v>IC0803602</v>
+        <v>IC0655501</v>
       </c>
       <c r="F44" s="1" t="str">
-        <v>페펜스튜디오 문구행사</v>
+        <v>냐냐온 스튜디오 문구행사</v>
       </c>
       <c r="G44" s="1">
-        <v>330000</v>
+        <v>380000</v>
       </c>
       <c r="H44" s="1" t="str">
         <v/>
       </c>
       <c r="I44" s="1">
-        <v>330000</v>
+        <v>380000</v>
       </c>
       <c r="J44" s="1">
-        <v>0.7274</v>
+        <v>0.7555</v>
       </c>
     </row>
     <row r="45">
@@ -32782,31 +33083,31 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="str">
-        <v>0816312</v>
+        <v>0803833</v>
       </c>
       <c r="C45" s="1" t="str">
-        <v>엠젯패밀리</v>
+        <v>모나미(특정매입)</v>
       </c>
       <c r="D45" s="1" t="str">
-        <v>문구</v>
+        <v>특정매입</v>
       </c>
       <c r="E45" s="1" t="str">
-        <v>IC0631200</v>
+        <v>IC0383301</v>
       </c>
       <c r="F45" s="1" t="str">
-        <v>엠젯패밀리 일반</v>
+        <v>모나미(특정매입) 시즌특가</v>
       </c>
       <c r="G45" s="1">
-        <v>380000</v>
-      </c>
-      <c r="H45" s="1">
-        <v>50000</v>
+        <v>370000</v>
+      </c>
+      <c r="H45" s="1" t="str">
+        <v/>
       </c>
       <c r="I45" s="1">
-        <v>330000</v>
+        <v>370000</v>
       </c>
       <c r="J45" s="1">
-        <v>0.7274</v>
+        <v>0.7357</v>
       </c>
     </row>
     <row r="46">
@@ -32814,31 +33115,31 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="str">
-        <v>0803267</v>
+        <v>0818036</v>
       </c>
       <c r="C46" s="1" t="str">
-        <v>플레플레</v>
+        <v>페펜스튜디오</v>
       </c>
       <c r="D46" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E46" s="1" t="str">
-        <v>IC0326701</v>
+        <v>IC0803601</v>
       </c>
       <c r="F46" s="1" t="str">
-        <v>플레플레 특가</v>
+        <v>페펜스튜디오 특가</v>
       </c>
       <c r="G46" s="1">
-        <v>320000</v>
+        <v>330000</v>
       </c>
       <c r="H46" s="1" t="str">
         <v/>
       </c>
       <c r="I46" s="1">
-        <v>320000</v>
+        <v>330000</v>
       </c>
       <c r="J46" s="1">
-        <v>0.7053</v>
+        <v>0.6561</v>
       </c>
     </row>
     <row r="47">
@@ -32846,31 +33147,31 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="str">
-        <v>0803267</v>
+        <v>0818036</v>
       </c>
       <c r="C47" s="1" t="str">
-        <v>플레플레</v>
+        <v>페펜스튜디오</v>
       </c>
       <c r="D47" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E47" s="1" t="str">
-        <v>IC0326702</v>
+        <v>IC0803602</v>
       </c>
       <c r="F47" s="1" t="str">
-        <v>플레플레 문구행사</v>
+        <v>페펜스튜디오 문구행사</v>
       </c>
       <c r="G47" s="1">
-        <v>320000</v>
+        <v>330000</v>
       </c>
       <c r="H47" s="1" t="str">
         <v/>
       </c>
       <c r="I47" s="1">
-        <v>320000</v>
+        <v>330000</v>
       </c>
       <c r="J47" s="1">
-        <v>0.7053</v>
+        <v>0.6561</v>
       </c>
     </row>
     <row r="48">
@@ -32878,31 +33179,31 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="str">
-        <v>0803186</v>
+        <v>0816312</v>
       </c>
       <c r="C48" s="1" t="str">
-        <v>아이코닉</v>
+        <v>엠젯패밀리</v>
       </c>
       <c r="D48" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E48" s="1" t="str">
-        <v>IC0318601</v>
+        <v>IC0631200</v>
       </c>
       <c r="F48" s="1" t="str">
-        <v>아이코닉 특가</v>
+        <v>엠젯패밀리 일반</v>
       </c>
       <c r="G48" s="1">
-        <v>290000</v>
-      </c>
-      <c r="H48" s="1" t="str">
-        <v/>
+        <v>380000</v>
+      </c>
+      <c r="H48" s="1">
+        <v>50000</v>
       </c>
       <c r="I48" s="1">
-        <v>290000</v>
+        <v>330000</v>
       </c>
       <c r="J48" s="1">
-        <v>0.6392</v>
+        <v>0.6561</v>
       </c>
     </row>
     <row r="49">
@@ -32910,31 +33211,31 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="str">
-        <v>0803186</v>
+        <v>0803267</v>
       </c>
       <c r="C49" s="1" t="str">
-        <v>아이코닉</v>
+        <v>플레플레</v>
       </c>
       <c r="D49" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E49" s="1" t="str">
-        <v>IC0318602</v>
+        <v>IC0326701</v>
       </c>
       <c r="F49" s="1" t="str">
-        <v>아이코닉 문구행사</v>
+        <v>플레플레 특가</v>
       </c>
       <c r="G49" s="1">
-        <v>290000</v>
+        <v>320000</v>
       </c>
       <c r="H49" s="1" t="str">
         <v/>
       </c>
       <c r="I49" s="1">
-        <v>290000</v>
+        <v>320000</v>
       </c>
       <c r="J49" s="1">
-        <v>0.6392</v>
+        <v>0.6362</v>
       </c>
     </row>
     <row r="50">
@@ -32942,31 +33243,31 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="str">
-        <v>0803159</v>
+        <v>0803267</v>
       </c>
       <c r="C50" s="1" t="str">
-        <v>안테나샵</v>
+        <v>플레플레</v>
       </c>
       <c r="D50" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E50" s="1" t="str">
-        <v>IC0315901</v>
+        <v>IC0326702</v>
       </c>
       <c r="F50" s="1" t="str">
-        <v>안테나샵 특가</v>
+        <v>플레플레 문구행사</v>
       </c>
       <c r="G50" s="1">
-        <v>290000</v>
+        <v>320000</v>
       </c>
       <c r="H50" s="1" t="str">
         <v/>
       </c>
       <c r="I50" s="1">
-        <v>290000</v>
+        <v>320000</v>
       </c>
       <c r="J50" s="1">
-        <v>0.6392</v>
+        <v>0.6362</v>
       </c>
     </row>
     <row r="51">
@@ -32974,19 +33275,19 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="str">
-        <v>0803159</v>
+        <v>0803186</v>
       </c>
       <c r="C51" s="1" t="str">
-        <v>안테나샵</v>
+        <v>아이코닉</v>
       </c>
       <c r="D51" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E51" s="1" t="str">
-        <v>IC0315902</v>
+        <v>IC0318601</v>
       </c>
       <c r="F51" s="1" t="str">
-        <v>안테나샵 문구행사</v>
+        <v>아이코닉 특가</v>
       </c>
       <c r="G51" s="1">
         <v>290000</v>
@@ -32998,7 +33299,7 @@
         <v>290000</v>
       </c>
       <c r="J51" s="1">
-        <v>0.6392</v>
+        <v>0.5766</v>
       </c>
     </row>
     <row r="52">
@@ -33006,19 +33307,19 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="str">
-        <v>0803527</v>
+        <v>0803186</v>
       </c>
       <c r="C52" s="1" t="str">
-        <v>프론티어통상</v>
+        <v>아이코닉</v>
       </c>
       <c r="D52" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E52" s="1" t="str">
-        <v>IC0352700</v>
+        <v>IC0318602</v>
       </c>
       <c r="F52" s="1" t="str">
-        <v>프론티어통상 일반</v>
+        <v>아이코닉 문구행사</v>
       </c>
       <c r="G52" s="1">
         <v>290000</v>
@@ -33030,7 +33331,7 @@
         <v>290000</v>
       </c>
       <c r="J52" s="1">
-        <v>0.6392</v>
+        <v>0.5766</v>
       </c>
     </row>
     <row r="53">
@@ -33038,19 +33339,19 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="str">
-        <v>01B0504</v>
+        <v>0803159</v>
       </c>
       <c r="C53" s="1" t="str">
-        <v>카카오엔터테인먼트</v>
+        <v>안테나샵</v>
       </c>
       <c r="D53" s="1" t="str">
-        <v>음반</v>
+        <v>문구</v>
       </c>
       <c r="E53" s="1" t="str">
-        <v>IB0050400</v>
+        <v>IC0315901</v>
       </c>
       <c r="F53" s="1" t="str">
-        <v>카카오엔터테인먼트 일반</v>
+        <v>안테나샵 특가</v>
       </c>
       <c r="G53" s="1">
         <v>290000</v>
@@ -33062,7 +33363,7 @@
         <v>290000</v>
       </c>
       <c r="J53" s="1">
-        <v>0.6392</v>
+        <v>0.5766</v>
       </c>
     </row>
     <row r="54">
@@ -33070,31 +33371,31 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="str">
-        <v>0803124</v>
+        <v>0803159</v>
       </c>
       <c r="C54" s="1" t="str">
-        <v>아톰상사(특정매입)</v>
+        <v>안테나샵</v>
       </c>
       <c r="D54" s="1" t="str">
-        <v>특정매입</v>
+        <v>문구</v>
       </c>
       <c r="E54" s="1" t="str">
-        <v>IC0312401</v>
+        <v>IC0315902</v>
       </c>
       <c r="F54" s="1" t="str">
-        <v>아톰상사(특정매입) 특정매입</v>
+        <v>안테나샵 문구행사</v>
       </c>
       <c r="G54" s="1">
-        <v>280000</v>
+        <v>290000</v>
       </c>
       <c r="H54" s="1" t="str">
         <v/>
       </c>
       <c r="I54" s="1">
-        <v>280000</v>
+        <v>290000</v>
       </c>
       <c r="J54" s="1">
-        <v>0.6171</v>
+        <v>0.5766</v>
       </c>
     </row>
     <row r="55">
@@ -33102,31 +33403,31 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="str">
-        <v>0803124</v>
+        <v>0803527</v>
       </c>
       <c r="C55" s="1" t="str">
-        <v>아톰상사(특정매입)</v>
+        <v>프론티어통상</v>
       </c>
       <c r="D55" s="1" t="str">
-        <v>특정매입</v>
+        <v>문구</v>
       </c>
       <c r="E55" s="1" t="str">
-        <v>IC0312402</v>
+        <v>IC0352700</v>
       </c>
       <c r="F55" s="1" t="str">
-        <v>아톰상사(특정매입) 시즌특가</v>
+        <v>프론티어통상 일반</v>
       </c>
       <c r="G55" s="1">
-        <v>280000</v>
+        <v>290000</v>
       </c>
       <c r="H55" s="1" t="str">
         <v/>
       </c>
       <c r="I55" s="1">
-        <v>280000</v>
+        <v>290000</v>
       </c>
       <c r="J55" s="1">
-        <v>0.6171</v>
+        <v>0.5766</v>
       </c>
     </row>
     <row r="56">
@@ -33134,31 +33435,31 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="str">
-        <v>0811795</v>
+        <v>01B0504</v>
       </c>
       <c r="C56" s="1" t="str">
-        <v>베르제마넷</v>
+        <v>카카오엔터테인먼트</v>
       </c>
       <c r="D56" s="1" t="str">
-        <v>문구</v>
+        <v>음반</v>
       </c>
       <c r="E56" s="1" t="str">
-        <v>IC0179501</v>
+        <v>IB0050400</v>
       </c>
       <c r="F56" s="1" t="str">
-        <v>베르제마넷 리미티드</v>
+        <v>카카오엔터테인먼트 일반</v>
       </c>
       <c r="G56" s="1">
-        <v>280000</v>
+        <v>290000</v>
       </c>
       <c r="H56" s="1" t="str">
         <v/>
       </c>
       <c r="I56" s="1">
-        <v>280000</v>
+        <v>290000</v>
       </c>
       <c r="J56" s="1">
-        <v>0.6171</v>
+        <v>0.5766</v>
       </c>
     </row>
     <row r="57">
@@ -33166,19 +33467,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="str">
-        <v>0811795</v>
+        <v>0803124</v>
       </c>
       <c r="C57" s="1" t="str">
-        <v>베르제마넷</v>
+        <v>아톰상사(특정매입)</v>
       </c>
       <c r="D57" s="1" t="str">
-        <v>문구</v>
+        <v>특정매입</v>
       </c>
       <c r="E57" s="1" t="str">
-        <v>IC0179502</v>
+        <v>IC0312401</v>
       </c>
       <c r="F57" s="1" t="str">
-        <v>베르제마넷 기획전</v>
+        <v>아톰상사(특정매입) 특정매입</v>
       </c>
       <c r="G57" s="1">
         <v>280000</v>
@@ -33190,7 +33491,7 @@
         <v>280000</v>
       </c>
       <c r="J57" s="1">
-        <v>0.6171</v>
+        <v>0.5567</v>
       </c>
     </row>
     <row r="58">
@@ -33198,19 +33499,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="str">
-        <v>0817225</v>
+        <v>0803124</v>
       </c>
       <c r="C58" s="1" t="str">
-        <v>도혜드로잉</v>
+        <v>아톰상사(특정매입)</v>
       </c>
       <c r="D58" s="1" t="str">
-        <v>문구</v>
+        <v>특정매입</v>
       </c>
       <c r="E58" s="1" t="str">
-        <v>IC0722500</v>
+        <v>IC0312402</v>
       </c>
       <c r="F58" s="1" t="str">
-        <v>도혜드로잉 일반</v>
+        <v>아톰상사(특정매입) 시즌특가</v>
       </c>
       <c r="G58" s="1">
         <v>280000</v>
@@ -33222,7 +33523,7 @@
         <v>280000</v>
       </c>
       <c r="J58" s="1">
-        <v>0.6171</v>
+        <v>0.5567</v>
       </c>
     </row>
     <row r="59">
@@ -33230,31 +33531,31 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="str">
-        <v>0816166</v>
+        <v>0811795</v>
       </c>
       <c r="C59" s="1" t="str">
-        <v>해밀</v>
+        <v>베르제마넷</v>
       </c>
       <c r="D59" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E59" s="1" t="str">
-        <v>IC0616600</v>
+        <v>IC0179501</v>
       </c>
       <c r="F59" s="1" t="str">
-        <v>해밀 일반</v>
+        <v>베르제마넷 리미티드</v>
       </c>
       <c r="G59" s="1">
-        <v>220000</v>
+        <v>280000</v>
       </c>
       <c r="H59" s="1" t="str">
         <v/>
       </c>
       <c r="I59" s="1">
-        <v>220000</v>
+        <v>280000</v>
       </c>
       <c r="J59" s="1">
-        <v>0.4849</v>
+        <v>0.5567</v>
       </c>
     </row>
     <row r="60">
@@ -33262,31 +33563,31 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="str">
-        <v>01B0478</v>
+        <v>0811795</v>
       </c>
       <c r="C60" s="1" t="str">
-        <v>와이지플러스</v>
+        <v>베르제마넷</v>
       </c>
       <c r="D60" s="1" t="str">
-        <v>음반</v>
+        <v>문구</v>
       </c>
       <c r="E60" s="1" t="str">
-        <v>IB0047800</v>
+        <v>IC0179502</v>
       </c>
       <c r="F60" s="1" t="str">
-        <v>와이지플러스 일반</v>
+        <v>베르제마넷 기획전</v>
       </c>
       <c r="G60" s="1">
-        <v>220000</v>
+        <v>280000</v>
       </c>
       <c r="H60" s="1" t="str">
         <v/>
       </c>
       <c r="I60" s="1">
-        <v>220000</v>
+        <v>280000</v>
       </c>
       <c r="J60" s="1">
-        <v>0.4849</v>
+        <v>0.5567</v>
       </c>
     </row>
     <row r="61">
@@ -33294,31 +33595,31 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="str">
-        <v>01B0470</v>
+        <v>0817225</v>
       </c>
       <c r="C61" s="1" t="str">
-        <v>드림어스컴퍼니</v>
+        <v>도혜드로잉</v>
       </c>
       <c r="D61" s="1" t="str">
-        <v>음반</v>
+        <v>문구</v>
       </c>
       <c r="E61" s="1" t="str">
-        <v>IB0047000</v>
+        <v>IC0722500</v>
       </c>
       <c r="F61" s="1" t="str">
-        <v>드림어스컴퍼니 일반</v>
+        <v>도혜드로잉 일반</v>
       </c>
       <c r="G61" s="1">
-        <v>220000</v>
+        <v>280000</v>
       </c>
       <c r="H61" s="1" t="str">
         <v/>
       </c>
       <c r="I61" s="1">
-        <v>220000</v>
+        <v>280000</v>
       </c>
       <c r="J61" s="1">
-        <v>0.4849</v>
+        <v>0.5567</v>
       </c>
     </row>
     <row r="62">
@@ -33326,31 +33627,31 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="str">
-        <v>0817604</v>
+        <v>0803229</v>
       </c>
       <c r="C62" s="1" t="str">
-        <v>비온뒤</v>
+        <v>웨이크업(wakup)</v>
       </c>
       <c r="D62" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E62" s="1" t="str">
-        <v>IC0760401</v>
+        <v>IC0322900</v>
       </c>
       <c r="F62" s="1" t="str">
-        <v>비온뒤 특가</v>
+        <v>웨이크업(wakup) 일반</v>
       </c>
       <c r="G62" s="1">
-        <v>210000</v>
+        <v>227600</v>
       </c>
       <c r="H62" s="1" t="str">
         <v/>
       </c>
       <c r="I62" s="1">
-        <v>210000</v>
+        <v>227600</v>
       </c>
       <c r="J62" s="1">
-        <v>0.4629</v>
+        <v>0.4525</v>
       </c>
     </row>
     <row r="63">
@@ -33358,31 +33659,31 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="str">
-        <v>0817604</v>
+        <v>0816166</v>
       </c>
       <c r="C63" s="1" t="str">
-        <v>비온뒤</v>
+        <v>해밀</v>
       </c>
       <c r="D63" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E63" s="1" t="str">
-        <v>IC0760402</v>
+        <v>IC0616600</v>
       </c>
       <c r="F63" s="1" t="str">
-        <v>비온뒤 문구행사</v>
+        <v>해밀 일반</v>
       </c>
       <c r="G63" s="1">
-        <v>210000</v>
+        <v>220000</v>
       </c>
       <c r="H63" s="1" t="str">
         <v/>
       </c>
       <c r="I63" s="1">
-        <v>210000</v>
+        <v>220000</v>
       </c>
       <c r="J63" s="1">
-        <v>0.4629</v>
+        <v>0.4374</v>
       </c>
     </row>
     <row r="64">
@@ -33390,31 +33691,31 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="str">
-        <v>0900224</v>
+        <v>01B0478</v>
       </c>
       <c r="C64" s="1" t="str">
-        <v>LIHIT LAB.,INC</v>
+        <v>와이지플러스</v>
       </c>
       <c r="D64" s="1" t="str">
-        <v>해외문구</v>
+        <v>음반</v>
       </c>
       <c r="E64" s="1" t="str">
-        <v>IC0022401</v>
+        <v>IB0047800</v>
       </c>
       <c r="F64" s="1" t="str">
-        <v>LIHIT LAB.,INC 베이직</v>
+        <v>와이지플러스 일반</v>
       </c>
       <c r="G64" s="1">
-        <v>200000</v>
+        <v>220000</v>
       </c>
       <c r="H64" s="1" t="str">
         <v/>
       </c>
       <c r="I64" s="1">
-        <v>200000</v>
+        <v>220000</v>
       </c>
       <c r="J64" s="1">
-        <v>0.4408</v>
+        <v>0.4374</v>
       </c>
     </row>
     <row r="65">
@@ -33422,31 +33723,31 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="str">
-        <v>0900224</v>
+        <v>01B0470</v>
       </c>
       <c r="C65" s="1" t="str">
-        <v>LIHIT LAB.,INC</v>
+        <v>드림어스컴퍼니</v>
       </c>
       <c r="D65" s="1" t="str">
-        <v>해외문구</v>
+        <v>음반</v>
       </c>
       <c r="E65" s="1" t="str">
-        <v>IC0022402</v>
+        <v>IB0047000</v>
       </c>
       <c r="F65" s="1" t="str">
-        <v>LIHIT LAB.,INC PB</v>
+        <v>드림어스컴퍼니 일반</v>
       </c>
       <c r="G65" s="1">
-        <v>200000</v>
+        <v>220000</v>
       </c>
       <c r="H65" s="1" t="str">
         <v/>
       </c>
       <c r="I65" s="1">
-        <v>200000</v>
+        <v>220000</v>
       </c>
       <c r="J65" s="1">
-        <v>0.4408</v>
+        <v>0.4374</v>
       </c>
     </row>
     <row r="66">
@@ -33454,31 +33755,31 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="str">
-        <v>0900224</v>
+        <v>0817604</v>
       </c>
       <c r="C66" s="1" t="str">
-        <v>LIHIT LAB.,INC</v>
+        <v>비온뒤</v>
       </c>
       <c r="D66" s="1" t="str">
-        <v>해외문구</v>
+        <v>문구</v>
       </c>
       <c r="E66" s="1" t="str">
-        <v>IC0022403</v>
+        <v>IC0760401</v>
       </c>
       <c r="F66" s="1" t="str">
-        <v>LIHIT LAB.,INC 리미티드</v>
+        <v>비온뒤 특가</v>
       </c>
       <c r="G66" s="1">
-        <v>200000</v>
+        <v>210000</v>
       </c>
       <c r="H66" s="1" t="str">
         <v/>
       </c>
       <c r="I66" s="1">
-        <v>200000</v>
+        <v>210000</v>
       </c>
       <c r="J66" s="1">
-        <v>0.4408</v>
+        <v>0.4175</v>
       </c>
     </row>
     <row r="67">
@@ -33486,31 +33787,31 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="str">
-        <v>0816903</v>
+        <v>0817604</v>
       </c>
       <c r="C67" s="1" t="str">
-        <v>더시호</v>
+        <v>비온뒤</v>
       </c>
       <c r="D67" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E67" s="1" t="str">
-        <v>IC0690301</v>
+        <v>IC0760402</v>
       </c>
       <c r="F67" s="1" t="str">
-        <v>더시호 증정</v>
+        <v>비온뒤 문구행사</v>
       </c>
       <c r="G67" s="1">
-        <v>200000</v>
+        <v>210000</v>
       </c>
       <c r="H67" s="1" t="str">
         <v/>
       </c>
       <c r="I67" s="1">
-        <v>200000</v>
+        <v>210000</v>
       </c>
       <c r="J67" s="1">
-        <v>0.4408</v>
+        <v>0.4175</v>
       </c>
     </row>
     <row r="68">
@@ -33518,19 +33819,19 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="str">
-        <v>0816903</v>
+        <v>0900224</v>
       </c>
       <c r="C68" s="1" t="str">
-        <v>더시호</v>
+        <v>LIHIT LAB.,INC</v>
       </c>
       <c r="D68" s="1" t="str">
-        <v>문구</v>
+        <v>해외문구</v>
       </c>
       <c r="E68" s="1" t="str">
-        <v>IC0690302</v>
+        <v>IC0022401</v>
       </c>
       <c r="F68" s="1" t="str">
-        <v>더시호 대표상품</v>
+        <v>LIHIT LAB.,INC 베이직</v>
       </c>
       <c r="G68" s="1">
         <v>200000</v>
@@ -33542,7 +33843,7 @@
         <v>200000</v>
       </c>
       <c r="J68" s="1">
-        <v>0.4408</v>
+        <v>0.3977</v>
       </c>
     </row>
     <row r="69">
@@ -33550,19 +33851,19 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="str">
-        <v>0816903</v>
+        <v>0900224</v>
       </c>
       <c r="C69" s="1" t="str">
-        <v>더시호</v>
+        <v>LIHIT LAB.,INC</v>
       </c>
       <c r="D69" s="1" t="str">
-        <v>문구</v>
+        <v>해외문구</v>
       </c>
       <c r="E69" s="1" t="str">
-        <v>IC0690303</v>
+        <v>IC0022402</v>
       </c>
       <c r="F69" s="1" t="str">
-        <v>더시호 특가</v>
+        <v>LIHIT LAB.,INC PB</v>
       </c>
       <c r="G69" s="1">
         <v>200000</v>
@@ -33574,7 +33875,7 @@
         <v>200000</v>
       </c>
       <c r="J69" s="1">
-        <v>0.4408</v>
+        <v>0.3977</v>
       </c>
     </row>
     <row r="70">
@@ -33582,19 +33883,19 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="str">
-        <v>0803527</v>
+        <v>0900224</v>
       </c>
       <c r="C70" s="1" t="str">
-        <v>프론티어통상</v>
+        <v>LIHIT LAB.,INC</v>
       </c>
       <c r="D70" s="1" t="str">
-        <v>문구</v>
+        <v>해외문구</v>
       </c>
       <c r="E70" s="1" t="str">
-        <v>IC0352701</v>
+        <v>IC0022403</v>
       </c>
       <c r="F70" s="1" t="str">
-        <v>프론티어통상 대표상품</v>
+        <v>LIHIT LAB.,INC 리미티드</v>
       </c>
       <c r="G70" s="1">
         <v>200000</v>
@@ -33606,7 +33907,7 @@
         <v>200000</v>
       </c>
       <c r="J70" s="1">
-        <v>0.4408</v>
+        <v>0.3977</v>
       </c>
     </row>
     <row r="71">
@@ -33614,31 +33915,31 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="str">
-        <v>0803187</v>
+        <v>0816903</v>
       </c>
       <c r="C71" s="1" t="str">
-        <v>칠삼이일디자인</v>
+        <v>더시호</v>
       </c>
       <c r="D71" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E71" s="1" t="str">
-        <v>IC0318701</v>
+        <v>IC0690301</v>
       </c>
       <c r="F71" s="1" t="str">
-        <v>칠삼이일디자인 증정</v>
+        <v>더시호 증정</v>
       </c>
       <c r="G71" s="1">
-        <v>190000</v>
+        <v>200000</v>
       </c>
       <c r="H71" s="1" t="str">
         <v/>
       </c>
       <c r="I71" s="1">
-        <v>190000</v>
+        <v>200000</v>
       </c>
       <c r="J71" s="1">
-        <v>0.4188</v>
+        <v>0.3977</v>
       </c>
     </row>
     <row r="72">
@@ -33646,31 +33947,31 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="str">
-        <v>0803187</v>
+        <v>0816903</v>
       </c>
       <c r="C72" s="1" t="str">
-        <v>칠삼이일디자인</v>
+        <v>더시호</v>
       </c>
       <c r="D72" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E72" s="1" t="str">
-        <v>IC0318702</v>
+        <v>IC0690302</v>
       </c>
       <c r="F72" s="1" t="str">
-        <v>칠삼이일디자인 대표상품</v>
+        <v>더시호 대표상품</v>
       </c>
       <c r="G72" s="1">
-        <v>190000</v>
+        <v>200000</v>
       </c>
       <c r="H72" s="1" t="str">
         <v/>
       </c>
       <c r="I72" s="1">
-        <v>190000</v>
+        <v>200000</v>
       </c>
       <c r="J72" s="1">
-        <v>0.4188</v>
+        <v>0.3977</v>
       </c>
     </row>
     <row r="73">
@@ -33678,31 +33979,31 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="str">
-        <v>0803187</v>
+        <v>0816903</v>
       </c>
       <c r="C73" s="1" t="str">
-        <v>칠삼이일디자인</v>
+        <v>더시호</v>
       </c>
       <c r="D73" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E73" s="1" t="str">
-        <v>IC0318703</v>
+        <v>IC0690303</v>
       </c>
       <c r="F73" s="1" t="str">
-        <v>칠삼이일디자인 특가</v>
+        <v>더시호 특가</v>
       </c>
       <c r="G73" s="1">
-        <v>190000</v>
+        <v>200000</v>
       </c>
       <c r="H73" s="1" t="str">
         <v/>
       </c>
       <c r="I73" s="1">
-        <v>190000</v>
+        <v>200000</v>
       </c>
       <c r="J73" s="1">
-        <v>0.4188</v>
+        <v>0.3977</v>
       </c>
     </row>
     <row r="74">
@@ -33710,31 +34011,31 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="str">
-        <v>0803825</v>
+        <v>0803527</v>
       </c>
       <c r="C74" s="1" t="str">
-        <v>정인통상</v>
+        <v>프론티어통상</v>
       </c>
       <c r="D74" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E74" s="1" t="str">
-        <v>IC0382501</v>
+        <v>IC0352701</v>
       </c>
       <c r="F74" s="1" t="str">
-        <v>정인통상 기획전</v>
+        <v>프론티어통상 대표상품</v>
       </c>
       <c r="G74" s="1">
-        <v>190000</v>
+        <v>200000</v>
       </c>
       <c r="H74" s="1" t="str">
         <v/>
       </c>
       <c r="I74" s="1">
-        <v>190000</v>
+        <v>200000</v>
       </c>
       <c r="J74" s="1">
-        <v>0.4188</v>
+        <v>0.3977</v>
       </c>
     </row>
     <row r="75">
@@ -33742,19 +34043,19 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="str">
-        <v>0803825</v>
+        <v>0803187</v>
       </c>
       <c r="C75" s="1" t="str">
-        <v>정인통상</v>
+        <v>칠삼이일디자인</v>
       </c>
       <c r="D75" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E75" s="1" t="str">
-        <v>IC0382502</v>
+        <v>IC0318701</v>
       </c>
       <c r="F75" s="1" t="str">
-        <v>정인통상 증정</v>
+        <v>칠삼이일디자인 증정</v>
       </c>
       <c r="G75" s="1">
         <v>190000</v>
@@ -33766,7 +34067,7 @@
         <v>190000</v>
       </c>
       <c r="J75" s="1">
-        <v>0.4188</v>
+        <v>0.3778</v>
       </c>
     </row>
     <row r="76">
@@ -33774,19 +34075,19 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="str">
-        <v>0817135</v>
+        <v>0803187</v>
       </c>
       <c r="C76" s="1" t="str">
-        <v>해피썬</v>
+        <v>칠삼이일디자인</v>
       </c>
       <c r="D76" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E76" s="1" t="str">
-        <v>IC0713500</v>
+        <v>IC0318702</v>
       </c>
       <c r="F76" s="1" t="str">
-        <v>해피썬 일반</v>
+        <v>칠삼이일디자인 대표상품</v>
       </c>
       <c r="G76" s="1">
         <v>190000</v>
@@ -33798,7 +34099,7 @@
         <v>190000</v>
       </c>
       <c r="J76" s="1">
-        <v>0.4188</v>
+        <v>0.3778</v>
       </c>
     </row>
     <row r="77">
@@ -33806,31 +34107,31 @@
         <v>76</v>
       </c>
       <c r="B77" s="1" t="str">
-        <v>0803222</v>
+        <v>0803187</v>
       </c>
       <c r="C77" s="1" t="str">
-        <v>아르디움</v>
+        <v>칠삼이일디자인</v>
       </c>
       <c r="D77" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E77" s="1" t="str">
-        <v>IC0322201</v>
+        <v>IC0318703</v>
       </c>
       <c r="F77" s="1" t="str">
-        <v>아르디움 기획전</v>
+        <v>칠삼이일디자인 특가</v>
       </c>
       <c r="G77" s="1">
-        <v>210000</v>
-      </c>
-      <c r="H77" s="1">
-        <v>30000</v>
+        <v>190000</v>
+      </c>
+      <c r="H77" s="1" t="str">
+        <v/>
       </c>
       <c r="I77" s="1">
-        <v>180000</v>
+        <v>190000</v>
       </c>
       <c r="J77" s="1">
-        <v>0.3967</v>
+        <v>0.3778</v>
       </c>
     </row>
     <row r="78">
@@ -33838,31 +34139,31 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="str">
-        <v>0803222</v>
+        <v>0803825</v>
       </c>
       <c r="C78" s="1" t="str">
-        <v>아르디움</v>
+        <v>정인통상</v>
       </c>
       <c r="D78" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E78" s="1" t="str">
-        <v>IC0322202</v>
+        <v>IC0382501</v>
       </c>
       <c r="F78" s="1" t="str">
-        <v>아르디움 증정</v>
+        <v>정인통상 기획전</v>
       </c>
       <c r="G78" s="1">
-        <v>210000</v>
-      </c>
-      <c r="H78" s="1">
-        <v>30000</v>
+        <v>190000</v>
+      </c>
+      <c r="H78" s="1" t="str">
+        <v/>
       </c>
       <c r="I78" s="1">
-        <v>180000</v>
+        <v>190000</v>
       </c>
       <c r="J78" s="1">
-        <v>0.3967</v>
+        <v>0.3778</v>
       </c>
     </row>
     <row r="79">
@@ -33870,31 +34171,31 @@
         <v>78</v>
       </c>
       <c r="B79" s="1" t="str">
-        <v>0803222</v>
+        <v>0803825</v>
       </c>
       <c r="C79" s="1" t="str">
-        <v>아르디움</v>
+        <v>정인통상</v>
       </c>
       <c r="D79" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E79" s="1" t="str">
-        <v>IC0322203</v>
+        <v>IC0382502</v>
       </c>
       <c r="F79" s="1" t="str">
-        <v>아르디움 대표상품</v>
+        <v>정인통상 증정</v>
       </c>
       <c r="G79" s="1">
-        <v>210000</v>
-      </c>
-      <c r="H79" s="1">
-        <v>30000</v>
+        <v>190000</v>
+      </c>
+      <c r="H79" s="1" t="str">
+        <v/>
       </c>
       <c r="I79" s="1">
-        <v>180000</v>
+        <v>190000</v>
       </c>
       <c r="J79" s="1">
-        <v>0.3967</v>
+        <v>0.3778</v>
       </c>
     </row>
     <row r="80">
@@ -33902,31 +34203,31 @@
         <v>79</v>
       </c>
       <c r="B80" s="1" t="str">
-        <v>0817528</v>
+        <v>0817135</v>
       </c>
       <c r="C80" s="1" t="str">
-        <v>누크코퍼레이션</v>
+        <v>해피썬</v>
       </c>
       <c r="D80" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E80" s="1" t="str">
-        <v>IC0752801</v>
+        <v>IC0713500</v>
       </c>
       <c r="F80" s="1" t="str">
-        <v>누크코퍼레이션 대표상품</v>
+        <v>해피썬 일반</v>
       </c>
       <c r="G80" s="1">
-        <v>180000</v>
+        <v>190000</v>
       </c>
       <c r="H80" s="1" t="str">
         <v/>
       </c>
       <c r="I80" s="1">
-        <v>180000</v>
+        <v>190000</v>
       </c>
       <c r="J80" s="1">
-        <v>0.3967</v>
+        <v>0.3778</v>
       </c>
     </row>
     <row r="81">
@@ -33934,31 +34235,31 @@
         <v>80</v>
       </c>
       <c r="B81" s="1" t="str">
-        <v>0817528</v>
+        <v>0803222</v>
       </c>
       <c r="C81" s="1" t="str">
-        <v>누크코퍼레이션</v>
+        <v>아르디움</v>
       </c>
       <c r="D81" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E81" s="1" t="str">
-        <v>IC0752802</v>
+        <v>IC0322201</v>
       </c>
       <c r="F81" s="1" t="str">
-        <v>누크코퍼레이션 특가</v>
+        <v>아르디움 기획전</v>
       </c>
       <c r="G81" s="1">
-        <v>180000</v>
-      </c>
-      <c r="H81" s="1" t="str">
-        <v/>
+        <v>210000</v>
+      </c>
+      <c r="H81" s="1">
+        <v>30000</v>
       </c>
       <c r="I81" s="1">
         <v>180000</v>
       </c>
       <c r="J81" s="1">
-        <v>0.3967</v>
+        <v>0.3579</v>
       </c>
     </row>
     <row r="82">
@@ -33966,31 +34267,31 @@
         <v>81</v>
       </c>
       <c r="B82" s="1" t="str">
-        <v>0817225</v>
+        <v>0803222</v>
       </c>
       <c r="C82" s="1" t="str">
-        <v>도혜드로잉</v>
+        <v>아르디움</v>
       </c>
       <c r="D82" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E82" s="1" t="str">
-        <v>IC0722501</v>
+        <v>IC0322202</v>
       </c>
       <c r="F82" s="1" t="str">
-        <v>도혜드로잉 정품</v>
+        <v>아르디움 증정</v>
       </c>
       <c r="G82" s="1">
-        <v>180000</v>
-      </c>
-      <c r="H82" s="1" t="str">
-        <v/>
+        <v>210000</v>
+      </c>
+      <c r="H82" s="1">
+        <v>30000</v>
       </c>
       <c r="I82" s="1">
         <v>180000</v>
       </c>
       <c r="J82" s="1">
-        <v>0.3967</v>
+        <v>0.3579</v>
       </c>
     </row>
     <row r="83">
@@ -33998,31 +34299,31 @@
         <v>82</v>
       </c>
       <c r="B83" s="1" t="str">
-        <v>0800334</v>
+        <v>0803222</v>
       </c>
       <c r="C83" s="1" t="str">
-        <v>아이비스코리아</v>
+        <v>아르디움</v>
       </c>
       <c r="D83" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E83" s="1" t="str">
-        <v>IC0033400</v>
+        <v>IC0322203</v>
       </c>
       <c r="F83" s="1" t="str">
-        <v>아이비스코리아 일반</v>
+        <v>아르디움 대표상품</v>
       </c>
       <c r="G83" s="1">
-        <v>180000</v>
-      </c>
-      <c r="H83" s="1" t="str">
-        <v/>
+        <v>210000</v>
+      </c>
+      <c r="H83" s="1">
+        <v>30000</v>
       </c>
       <c r="I83" s="1">
         <v>180000</v>
       </c>
       <c r="J83" s="1">
-        <v>0.3967</v>
+        <v>0.3579</v>
       </c>
     </row>
     <row r="84">
@@ -34030,31 +34331,31 @@
         <v>83</v>
       </c>
       <c r="B84" s="1" t="str">
-        <v>0816796</v>
+        <v>0817528</v>
       </c>
       <c r="C84" s="1" t="str">
-        <v>마이누</v>
+        <v>누크코퍼레이션</v>
       </c>
       <c r="D84" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E84" s="1" t="str">
-        <v>IC0679601</v>
+        <v>IC0752801</v>
       </c>
       <c r="F84" s="1" t="str">
-        <v>마이누 정품</v>
+        <v>누크코퍼레이션 대표상품</v>
       </c>
       <c r="G84" s="1">
-        <v>170000</v>
+        <v>180000</v>
       </c>
       <c r="H84" s="1" t="str">
         <v/>
       </c>
       <c r="I84" s="1">
-        <v>170000</v>
+        <v>180000</v>
       </c>
       <c r="J84" s="1">
-        <v>0.3747</v>
+        <v>0.3579</v>
       </c>
     </row>
     <row r="85">
@@ -34062,31 +34363,31 @@
         <v>84</v>
       </c>
       <c r="B85" s="1" t="str">
-        <v>0816796</v>
+        <v>0817528</v>
       </c>
       <c r="C85" s="1" t="str">
-        <v>마이누</v>
+        <v>누크코퍼레이션</v>
       </c>
       <c r="D85" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E85" s="1" t="str">
-        <v>IC0679602</v>
+        <v>IC0752802</v>
       </c>
       <c r="F85" s="1" t="str">
-        <v>마이누 베이직</v>
+        <v>누크코퍼레이션 특가</v>
       </c>
       <c r="G85" s="1">
-        <v>170000</v>
+        <v>180000</v>
       </c>
       <c r="H85" s="1" t="str">
         <v/>
       </c>
       <c r="I85" s="1">
-        <v>170000</v>
+        <v>180000</v>
       </c>
       <c r="J85" s="1">
-        <v>0.3747</v>
+        <v>0.3579</v>
       </c>
     </row>
     <row r="86">
@@ -34094,31 +34395,31 @@
         <v>85</v>
       </c>
       <c r="B86" s="1" t="str">
-        <v>0816796</v>
+        <v>0817225</v>
       </c>
       <c r="C86" s="1" t="str">
-        <v>마이누</v>
+        <v>도혜드로잉</v>
       </c>
       <c r="D86" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E86" s="1" t="str">
-        <v>IC0679603</v>
+        <v>IC0722501</v>
       </c>
       <c r="F86" s="1" t="str">
-        <v>마이누 PB</v>
+        <v>도혜드로잉 정품</v>
       </c>
       <c r="G86" s="1">
-        <v>170000</v>
+        <v>180000</v>
       </c>
       <c r="H86" s="1" t="str">
         <v/>
       </c>
       <c r="I86" s="1">
-        <v>170000</v>
+        <v>180000</v>
       </c>
       <c r="J86" s="1">
-        <v>0.3747</v>
+        <v>0.3579</v>
       </c>
     </row>
     <row r="87">
@@ -34126,31 +34427,31 @@
         <v>86</v>
       </c>
       <c r="B87" s="1" t="str">
-        <v>0803255</v>
+        <v>0800334</v>
       </c>
       <c r="C87" s="1" t="str">
-        <v>모닝글로리</v>
+        <v>아이비스코리아</v>
       </c>
       <c r="D87" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E87" s="1" t="str">
-        <v>IC0325501</v>
+        <v>IC0033400</v>
       </c>
       <c r="F87" s="1" t="str">
-        <v>모닝글로리 베이직</v>
+        <v>아이비스코리아 일반</v>
       </c>
       <c r="G87" s="1">
-        <v>160000</v>
+        <v>180000</v>
       </c>
       <c r="H87" s="1" t="str">
         <v/>
       </c>
       <c r="I87" s="1">
-        <v>160000</v>
+        <v>180000</v>
       </c>
       <c r="J87" s="1">
-        <v>0.3527</v>
+        <v>0.3579</v>
       </c>
     </row>
     <row r="88">
@@ -34158,31 +34459,31 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="str">
-        <v>0803255</v>
+        <v>0816796</v>
       </c>
       <c r="C88" s="1" t="str">
-        <v>모닝글로리</v>
+        <v>마이누</v>
       </c>
       <c r="D88" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E88" s="1" t="str">
-        <v>IC0325502</v>
+        <v>IC0679601</v>
       </c>
       <c r="F88" s="1" t="str">
-        <v>모닝글로리 PB</v>
+        <v>마이누 정품</v>
       </c>
       <c r="G88" s="1">
-        <v>160000</v>
+        <v>170000</v>
       </c>
       <c r="H88" s="1" t="str">
         <v/>
       </c>
       <c r="I88" s="1">
-        <v>160000</v>
+        <v>170000</v>
       </c>
       <c r="J88" s="1">
-        <v>0.3527</v>
+        <v>0.338</v>
       </c>
     </row>
     <row r="89">
@@ -34190,31 +34491,31 @@
         <v>88</v>
       </c>
       <c r="B89" s="1" t="str">
-        <v>0803255</v>
+        <v>0816796</v>
       </c>
       <c r="C89" s="1" t="str">
-        <v>모닝글로리</v>
+        <v>마이누</v>
       </c>
       <c r="D89" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E89" s="1" t="str">
-        <v>IC0325503</v>
+        <v>IC0679602</v>
       </c>
       <c r="F89" s="1" t="str">
-        <v>모닝글로리 리미티드</v>
+        <v>마이누 베이직</v>
       </c>
       <c r="G89" s="1">
-        <v>160000</v>
+        <v>170000</v>
       </c>
       <c r="H89" s="1" t="str">
         <v/>
       </c>
       <c r="I89" s="1">
-        <v>160000</v>
+        <v>170000</v>
       </c>
       <c r="J89" s="1">
-        <v>0.3527</v>
+        <v>0.338</v>
       </c>
     </row>
     <row r="90">
@@ -34222,31 +34523,31 @@
         <v>89</v>
       </c>
       <c r="B90" s="1" t="str">
-        <v>0803255</v>
+        <v>0816796</v>
       </c>
       <c r="C90" s="1" t="str">
-        <v>모닝글로리</v>
+        <v>마이누</v>
       </c>
       <c r="D90" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E90" s="1" t="str">
-        <v>IC0325504</v>
+        <v>IC0679603</v>
       </c>
       <c r="F90" s="1" t="str">
-        <v>모닝글로리 기획전</v>
+        <v>마이누 PB</v>
       </c>
       <c r="G90" s="1">
-        <v>160000</v>
+        <v>170000</v>
       </c>
       <c r="H90" s="1" t="str">
         <v/>
       </c>
       <c r="I90" s="1">
-        <v>160000</v>
+        <v>170000</v>
       </c>
       <c r="J90" s="1">
-        <v>0.3527</v>
+        <v>0.338</v>
       </c>
     </row>
     <row r="91">
@@ -34254,31 +34555,31 @@
         <v>90</v>
       </c>
       <c r="B91" s="1" t="str">
-        <v>0807497</v>
+        <v>0803288</v>
       </c>
       <c r="C91" s="1" t="str">
-        <v>학산문화사</v>
+        <v>명성코리아</v>
       </c>
       <c r="D91" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E91" s="1" t="str">
-        <v>IC0749700</v>
+        <v>IC0328800</v>
       </c>
       <c r="F91" s="1" t="str">
-        <v>학산문화사 일반</v>
+        <v>명성코리아 일반</v>
       </c>
       <c r="G91" s="1">
-        <v>160000</v>
+        <v>166950</v>
       </c>
       <c r="H91" s="1" t="str">
         <v/>
       </c>
       <c r="I91" s="1">
-        <v>160000</v>
+        <v>166950</v>
       </c>
       <c r="J91" s="1">
-        <v>0.3527</v>
+        <v>0.3319</v>
       </c>
     </row>
     <row r="92">
@@ -34286,31 +34587,31 @@
         <v>91</v>
       </c>
       <c r="B92" s="1" t="str">
-        <v>0900216</v>
+        <v>0803255</v>
       </c>
       <c r="C92" s="1" t="str">
-        <v>LEUCHTTURM</v>
+        <v>모닝글로리</v>
       </c>
       <c r="D92" s="1" t="str">
-        <v>해외문구</v>
+        <v>문구</v>
       </c>
       <c r="E92" s="1" t="str">
-        <v>IC0021601</v>
+        <v>IC0325501</v>
       </c>
       <c r="F92" s="1" t="str">
-        <v>LEUCHTTURM 증정</v>
+        <v>모닝글로리 베이직</v>
       </c>
       <c r="G92" s="1">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="H92" s="1" t="str">
         <v/>
       </c>
       <c r="I92" s="1">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="J92" s="1">
-        <v>0.3306</v>
+        <v>0.3181</v>
       </c>
     </row>
     <row r="93">
@@ -34318,31 +34619,31 @@
         <v>92</v>
       </c>
       <c r="B93" s="1" t="str">
-        <v>0900216</v>
+        <v>0803255</v>
       </c>
       <c r="C93" s="1" t="str">
-        <v>LEUCHTTURM</v>
+        <v>모닝글로리</v>
       </c>
       <c r="D93" s="1" t="str">
-        <v>해외문구</v>
+        <v>문구</v>
       </c>
       <c r="E93" s="1" t="str">
-        <v>IC0021602</v>
+        <v>IC0325502</v>
       </c>
       <c r="F93" s="1" t="str">
-        <v>LEUCHTTURM 대표상품</v>
+        <v>모닝글로리 PB</v>
       </c>
       <c r="G93" s="1">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="H93" s="1" t="str">
         <v/>
       </c>
       <c r="I93" s="1">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="J93" s="1">
-        <v>0.3306</v>
+        <v>0.3181</v>
       </c>
     </row>
     <row r="94">
@@ -34350,31 +34651,31 @@
         <v>93</v>
       </c>
       <c r="B94" s="1" t="str">
-        <v>0900216</v>
+        <v>0803255</v>
       </c>
       <c r="C94" s="1" t="str">
-        <v>LEUCHTTURM</v>
+        <v>모닝글로리</v>
       </c>
       <c r="D94" s="1" t="str">
-        <v>해외문구</v>
+        <v>문구</v>
       </c>
       <c r="E94" s="1" t="str">
-        <v>IC0021603</v>
+        <v>IC0325503</v>
       </c>
       <c r="F94" s="1" t="str">
-        <v>LEUCHTTURM 특가</v>
+        <v>모닝글로리 리미티드</v>
       </c>
       <c r="G94" s="1">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="H94" s="1" t="str">
         <v/>
       </c>
       <c r="I94" s="1">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="J94" s="1">
-        <v>0.3306</v>
+        <v>0.3181</v>
       </c>
     </row>
     <row r="95">
@@ -34382,31 +34683,31 @@
         <v>94</v>
       </c>
       <c r="B95" s="1" t="str">
-        <v>0900216</v>
+        <v>0803255</v>
       </c>
       <c r="C95" s="1" t="str">
-        <v>LEUCHTTURM</v>
+        <v>모닝글로리</v>
       </c>
       <c r="D95" s="1" t="str">
-        <v>해외문구</v>
+        <v>문구</v>
       </c>
       <c r="E95" s="1" t="str">
-        <v>IC0021604</v>
+        <v>IC0325504</v>
       </c>
       <c r="F95" s="1" t="str">
-        <v>LEUCHTTURM 문구행사</v>
+        <v>모닝글로리 기획전</v>
       </c>
       <c r="G95" s="1">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="H95" s="1" t="str">
         <v/>
       </c>
       <c r="I95" s="1">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="J95" s="1">
-        <v>0.3306</v>
+        <v>0.3181</v>
       </c>
     </row>
     <row r="96">
@@ -34414,31 +34715,31 @@
         <v>95</v>
       </c>
       <c r="B96" s="1" t="str">
-        <v>0807485</v>
+        <v>0807497</v>
       </c>
       <c r="C96" s="1" t="str">
-        <v>대시앤도트</v>
+        <v>학산문화사</v>
       </c>
       <c r="D96" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E96" s="1" t="str">
-        <v>IC0748500</v>
+        <v>IC0749700</v>
       </c>
       <c r="F96" s="1" t="str">
-        <v>대시앤도트 일반</v>
+        <v>학산문화사 일반</v>
       </c>
       <c r="G96" s="1">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="H96" s="1" t="str">
         <v/>
       </c>
       <c r="I96" s="1">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="J96" s="1">
-        <v>0.3306</v>
+        <v>0.3181</v>
       </c>
     </row>
     <row r="97">
@@ -34446,19 +34747,19 @@
         <v>96</v>
       </c>
       <c r="B97" s="1" t="str">
-        <v>0807481</v>
+        <v>0900216</v>
       </c>
       <c r="C97" s="1" t="str">
-        <v>골드디자인</v>
+        <v>LEUCHTTURM</v>
       </c>
       <c r="D97" s="1" t="str">
-        <v>문구</v>
+        <v>해외문구</v>
       </c>
       <c r="E97" s="1" t="str">
-        <v>IC0748100</v>
+        <v>IC0021601</v>
       </c>
       <c r="F97" s="1" t="str">
-        <v>골드디자인 일반</v>
+        <v>LEUCHTTURM 증정</v>
       </c>
       <c r="G97" s="1">
         <v>150000</v>
@@ -34470,7 +34771,7 @@
         <v>150000</v>
       </c>
       <c r="J97" s="1">
-        <v>0.3306</v>
+        <v>0.2982</v>
       </c>
     </row>
     <row r="98">
@@ -34478,31 +34779,31 @@
         <v>97</v>
       </c>
       <c r="B98" s="1" t="str">
-        <v>01B0470</v>
+        <v>0900216</v>
       </c>
       <c r="C98" s="1" t="str">
-        <v>드림어스컴퍼니</v>
+        <v>LEUCHTTURM</v>
       </c>
       <c r="D98" s="1" t="str">
-        <v>음반</v>
+        <v>해외문구</v>
       </c>
       <c r="E98" s="1" t="str">
-        <v>IB0047001</v>
+        <v>IC0021602</v>
       </c>
       <c r="F98" s="1" t="str">
-        <v>드림어스컴퍼니 해외음반</v>
+        <v>LEUCHTTURM 대표상품</v>
       </c>
       <c r="G98" s="1">
-        <v>140000</v>
+        <v>150000</v>
       </c>
       <c r="H98" s="1" t="str">
         <v/>
       </c>
       <c r="I98" s="1">
-        <v>140000</v>
+        <v>150000</v>
       </c>
       <c r="J98" s="1">
-        <v>0.3086</v>
+        <v>0.2982</v>
       </c>
     </row>
     <row r="99">
@@ -34510,31 +34811,31 @@
         <v>98</v>
       </c>
       <c r="B99" s="1" t="str">
-        <v>0900252</v>
+        <v>0900216</v>
       </c>
       <c r="C99" s="1" t="str">
-        <v>HIGHTIDE CO.,LTD</v>
+        <v>LEUCHTTURM</v>
       </c>
       <c r="D99" s="1" t="str">
         <v>해외문구</v>
       </c>
       <c r="E99" s="1" t="str">
-        <v>IC0025201</v>
+        <v>IC0021603</v>
       </c>
       <c r="F99" s="1" t="str">
-        <v>HIGHTIDE CO.,LTD 문구행사</v>
+        <v>LEUCHTTURM 특가</v>
       </c>
       <c r="G99" s="1">
         <v>150000</v>
       </c>
-      <c r="H99" s="1">
-        <v>20000</v>
+      <c r="H99" s="1" t="str">
+        <v/>
       </c>
       <c r="I99" s="1">
-        <v>130000</v>
+        <v>150000</v>
       </c>
       <c r="J99" s="1">
-        <v>0.2865</v>
+        <v>0.2982</v>
       </c>
     </row>
     <row r="100">
@@ -34542,31 +34843,31 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="str">
-        <v>0900252</v>
+        <v>0900216</v>
       </c>
       <c r="C100" s="1" t="str">
-        <v>HIGHTIDE CO.,LTD</v>
+        <v>LEUCHTTURM</v>
       </c>
       <c r="D100" s="1" t="str">
         <v>해외문구</v>
       </c>
       <c r="E100" s="1" t="str">
-        <v>IC0025202</v>
+        <v>IC0021604</v>
       </c>
       <c r="F100" s="1" t="str">
-        <v>HIGHTIDE CO.,LTD 정품</v>
+        <v>LEUCHTTURM 문구행사</v>
       </c>
       <c r="G100" s="1">
         <v>150000</v>
       </c>
-      <c r="H100" s="1">
-        <v>20000</v>
+      <c r="H100" s="1" t="str">
+        <v/>
       </c>
       <c r="I100" s="1">
-        <v>130000</v>
+        <v>150000</v>
       </c>
       <c r="J100" s="1">
-        <v>0.2865</v>
+        <v>0.2982</v>
       </c>
     </row>
     <row r="101">
@@ -34574,31 +34875,31 @@
         <v>100</v>
       </c>
       <c r="B101" s="1" t="str">
-        <v>0900252</v>
+        <v>0807485</v>
       </c>
       <c r="C101" s="1" t="str">
-        <v>HIGHTIDE CO.,LTD</v>
+        <v>대시앤도트</v>
       </c>
       <c r="D101" s="1" t="str">
-        <v>해외문구</v>
+        <v>문구</v>
       </c>
       <c r="E101" s="1" t="str">
-        <v>IC0025203</v>
+        <v>IC0748500</v>
       </c>
       <c r="F101" s="1" t="str">
-        <v>HIGHTIDE CO.,LTD 베이직</v>
+        <v>대시앤도트 일반</v>
       </c>
       <c r="G101" s="1">
         <v>150000</v>
       </c>
-      <c r="H101" s="1">
-        <v>20000</v>
+      <c r="H101" s="1" t="str">
+        <v/>
       </c>
       <c r="I101" s="1">
-        <v>130000</v>
+        <v>150000</v>
       </c>
       <c r="J101" s="1">
-        <v>0.2865</v>
+        <v>0.2982</v>
       </c>
     </row>
     <row r="102">
@@ -34606,31 +34907,31 @@
         <v>101</v>
       </c>
       <c r="B102" s="1" t="str">
-        <v>0900252</v>
+        <v>0807481</v>
       </c>
       <c r="C102" s="1" t="str">
-        <v>HIGHTIDE CO.,LTD</v>
+        <v>골드디자인</v>
       </c>
       <c r="D102" s="1" t="str">
-        <v>해외문구</v>
+        <v>문구</v>
       </c>
       <c r="E102" s="1" t="str">
-        <v>IC0025204</v>
+        <v>IC0748100</v>
       </c>
       <c r="F102" s="1" t="str">
-        <v>HIGHTIDE CO.,LTD PB</v>
+        <v>골드디자인 일반</v>
       </c>
       <c r="G102" s="1">
         <v>150000</v>
       </c>
-      <c r="H102" s="1">
-        <v>20000</v>
+      <c r="H102" s="1" t="str">
+        <v/>
       </c>
       <c r="I102" s="1">
-        <v>130000</v>
+        <v>150000</v>
       </c>
       <c r="J102" s="1">
-        <v>0.2865</v>
+        <v>0.2982</v>
       </c>
     </row>
     <row r="103">
@@ -34638,31 +34939,31 @@
         <v>102</v>
       </c>
       <c r="B103" s="1" t="str">
-        <v>0803690</v>
+        <v>01B0470</v>
       </c>
       <c r="C103" s="1" t="str">
-        <v>인디고</v>
+        <v>드림어스컴퍼니</v>
       </c>
       <c r="D103" s="1" t="str">
-        <v>문구</v>
+        <v>음반</v>
       </c>
       <c r="E103" s="1" t="str">
-        <v>IC0369001</v>
+        <v>IB0047001</v>
       </c>
       <c r="F103" s="1" t="str">
-        <v>인디고 기획전</v>
+        <v>드림어스컴퍼니 해외음반</v>
       </c>
       <c r="G103" s="1">
-        <v>130000</v>
+        <v>140000</v>
       </c>
       <c r="H103" s="1" t="str">
         <v/>
       </c>
       <c r="I103" s="1">
-        <v>130000</v>
+        <v>140000</v>
       </c>
       <c r="J103" s="1">
-        <v>0.2865</v>
+        <v>0.2784</v>
       </c>
     </row>
     <row r="104">
@@ -34670,31 +34971,31 @@
         <v>103</v>
       </c>
       <c r="B104" s="1" t="str">
-        <v>0803690</v>
+        <v>0900252</v>
       </c>
       <c r="C104" s="1" t="str">
-        <v>인디고</v>
+        <v>HIGHTIDE CO.,LTD</v>
       </c>
       <c r="D104" s="1" t="str">
-        <v>문구</v>
+        <v>해외문구</v>
       </c>
       <c r="E104" s="1" t="str">
-        <v>IC0369002</v>
+        <v>IC0025201</v>
       </c>
       <c r="F104" s="1" t="str">
-        <v>인디고 증정</v>
+        <v>HIGHTIDE CO.,LTD 문구행사</v>
       </c>
       <c r="G104" s="1">
-        <v>130000</v>
-      </c>
-      <c r="H104" s="1" t="str">
-        <v/>
+        <v>150000</v>
+      </c>
+      <c r="H104" s="1">
+        <v>20000</v>
       </c>
       <c r="I104" s="1">
         <v>130000</v>
       </c>
       <c r="J104" s="1">
-        <v>0.2865</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="105">
@@ -34702,31 +35003,31 @@
         <v>104</v>
       </c>
       <c r="B105" s="1" t="str">
-        <v>0817135</v>
+        <v>0900252</v>
       </c>
       <c r="C105" s="1" t="str">
-        <v>해피썬</v>
+        <v>HIGHTIDE CO.,LTD</v>
       </c>
       <c r="D105" s="1" t="str">
-        <v>문구</v>
+        <v>해외문구</v>
       </c>
       <c r="E105" s="1" t="str">
-        <v>IC0713501</v>
+        <v>IC0025202</v>
       </c>
       <c r="F105" s="1" t="str">
-        <v>해피썬 대표상품</v>
+        <v>HIGHTIDE CO.,LTD 정품</v>
       </c>
       <c r="G105" s="1">
-        <v>130000</v>
-      </c>
-      <c r="H105" s="1" t="str">
-        <v/>
+        <v>150000</v>
+      </c>
+      <c r="H105" s="1">
+        <v>20000</v>
       </c>
       <c r="I105" s="1">
         <v>130000</v>
       </c>
       <c r="J105" s="1">
-        <v>0.2865</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="106">
@@ -34734,31 +35035,31 @@
         <v>105</v>
       </c>
       <c r="B106" s="1" t="str">
-        <v>0816525</v>
+        <v>0900252</v>
       </c>
       <c r="C106" s="1" t="str">
-        <v>루카랩컴퍼니</v>
+        <v>HIGHTIDE CO.,LTD</v>
       </c>
       <c r="D106" s="1" t="str">
-        <v>문구</v>
+        <v>해외문구</v>
       </c>
       <c r="E106" s="1" t="str">
-        <v>IC0652501</v>
+        <v>IC0025203</v>
       </c>
       <c r="F106" s="1" t="str">
-        <v>루카랩컴퍼니 증정</v>
+        <v>HIGHTIDE CO.,LTD 베이직</v>
       </c>
       <c r="G106" s="1">
-        <v>120000</v>
-      </c>
-      <c r="H106" s="1" t="str">
-        <v/>
+        <v>150000</v>
+      </c>
+      <c r="H106" s="1">
+        <v>20000</v>
       </c>
       <c r="I106" s="1">
-        <v>120000</v>
+        <v>130000</v>
       </c>
       <c r="J106" s="1">
-        <v>0.2645</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="107">
@@ -34766,31 +35067,31 @@
         <v>106</v>
       </c>
       <c r="B107" s="1" t="str">
-        <v>0816525</v>
+        <v>0900252</v>
       </c>
       <c r="C107" s="1" t="str">
-        <v>루카랩컴퍼니</v>
+        <v>HIGHTIDE CO.,LTD</v>
       </c>
       <c r="D107" s="1" t="str">
-        <v>문구</v>
+        <v>해외문구</v>
       </c>
       <c r="E107" s="1" t="str">
-        <v>IC0652502</v>
+        <v>IC0025204</v>
       </c>
       <c r="F107" s="1" t="str">
-        <v>루카랩컴퍼니 대표상품</v>
+        <v>HIGHTIDE CO.,LTD PB</v>
       </c>
       <c r="G107" s="1">
-        <v>120000</v>
-      </c>
-      <c r="H107" s="1" t="str">
-        <v/>
+        <v>150000</v>
+      </c>
+      <c r="H107" s="1">
+        <v>20000</v>
       </c>
       <c r="I107" s="1">
-        <v>120000</v>
+        <v>130000</v>
       </c>
       <c r="J107" s="1">
-        <v>0.2645</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="108">
@@ -34798,31 +35099,31 @@
         <v>107</v>
       </c>
       <c r="B108" s="1" t="str">
-        <v>0816525</v>
+        <v>0803690</v>
       </c>
       <c r="C108" s="1" t="str">
-        <v>루카랩컴퍼니</v>
+        <v>인디고</v>
       </c>
       <c r="D108" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E108" s="1" t="str">
-        <v>IC0652503</v>
+        <v>IC0369001</v>
       </c>
       <c r="F108" s="1" t="str">
-        <v>루카랩컴퍼니 특가</v>
+        <v>인디고 기획전</v>
       </c>
       <c r="G108" s="1">
-        <v>120000</v>
+        <v>130000</v>
       </c>
       <c r="H108" s="1" t="str">
         <v/>
       </c>
       <c r="I108" s="1">
-        <v>120000</v>
+        <v>130000</v>
       </c>
       <c r="J108" s="1">
-        <v>0.2645</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="109">
@@ -34830,31 +35131,31 @@
         <v>108</v>
       </c>
       <c r="B109" s="1" t="str">
-        <v>0803303</v>
+        <v>0803690</v>
       </c>
       <c r="C109" s="1" t="str">
-        <v>이투컬렉션</v>
+        <v>인디고</v>
       </c>
       <c r="D109" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E109" s="1" t="str">
-        <v>IC0330300</v>
+        <v>IC0369002</v>
       </c>
       <c r="F109" s="1" t="str">
-        <v>이투컬렉션 일반</v>
+        <v>인디고 증정</v>
       </c>
       <c r="G109" s="1">
-        <v>120000</v>
+        <v>130000</v>
       </c>
       <c r="H109" s="1" t="str">
         <v/>
       </c>
       <c r="I109" s="1">
-        <v>120000</v>
+        <v>130000</v>
       </c>
       <c r="J109" s="1">
-        <v>0.2645</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="110">
@@ -34862,31 +35163,31 @@
         <v>109</v>
       </c>
       <c r="B110" s="1" t="str">
-        <v>0816312</v>
+        <v>0817135</v>
       </c>
       <c r="C110" s="1" t="str">
-        <v>엠젯패밀리</v>
+        <v>해피썬</v>
       </c>
       <c r="D110" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E110" s="1" t="str">
-        <v>IC0631201</v>
+        <v>IC0713501</v>
       </c>
       <c r="F110" s="1" t="str">
-        <v>엠젯패밀리 PB</v>
+        <v>해피썬 대표상품</v>
       </c>
       <c r="G110" s="1">
         <v>130000</v>
       </c>
-      <c r="H110" s="1">
-        <v>20000</v>
+      <c r="H110" s="1" t="str">
+        <v/>
       </c>
       <c r="I110" s="1">
-        <v>110000</v>
+        <v>130000</v>
       </c>
       <c r="J110" s="1">
-        <v>0.2425</v>
+        <v>0.2585</v>
       </c>
     </row>
     <row r="111">
@@ -34894,31 +35195,31 @@
         <v>110</v>
       </c>
       <c r="B111" s="1" t="str">
-        <v>0816312</v>
+        <v>0816525</v>
       </c>
       <c r="C111" s="1" t="str">
-        <v>엠젯패밀리</v>
+        <v>루카랩컴퍼니</v>
       </c>
       <c r="D111" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E111" s="1" t="str">
-        <v>IC0631202</v>
+        <v>IC0652501</v>
       </c>
       <c r="F111" s="1" t="str">
-        <v>엠젯패밀리 리미티드</v>
+        <v>루카랩컴퍼니 증정</v>
       </c>
       <c r="G111" s="1">
-        <v>130000</v>
-      </c>
-      <c r="H111" s="1">
-        <v>20000</v>
+        <v>120000</v>
+      </c>
+      <c r="H111" s="1" t="str">
+        <v/>
       </c>
       <c r="I111" s="1">
-        <v>110000</v>
+        <v>120000</v>
       </c>
       <c r="J111" s="1">
-        <v>0.2425</v>
+        <v>0.2386</v>
       </c>
     </row>
     <row r="112">
@@ -34926,31 +35227,31 @@
         <v>111</v>
       </c>
       <c r="B112" s="1" t="str">
-        <v>0807497</v>
+        <v>0816525</v>
       </c>
       <c r="C112" s="1" t="str">
-        <v>학산문화사</v>
+        <v>루카랩컴퍼니</v>
       </c>
       <c r="D112" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E112" s="1" t="str">
-        <v>IC0749701</v>
+        <v>IC0652502</v>
       </c>
       <c r="F112" s="1" t="str">
-        <v>학산문화사 베이직</v>
+        <v>루카랩컴퍼니 대표상품</v>
       </c>
       <c r="G112" s="1">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="H112" s="1" t="str">
         <v/>
       </c>
       <c r="I112" s="1">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="J112" s="1">
-        <v>0.2204</v>
+        <v>0.2386</v>
       </c>
     </row>
     <row r="113">
@@ -34958,31 +35259,31 @@
         <v>112</v>
       </c>
       <c r="B113" s="1" t="str">
-        <v>0812988</v>
+        <v>0816525</v>
       </c>
       <c r="C113" s="1" t="str">
-        <v>모트모트</v>
+        <v>루카랩컴퍼니</v>
       </c>
       <c r="D113" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E113" s="1" t="str">
-        <v>IC0298800</v>
+        <v>IC0652503</v>
       </c>
       <c r="F113" s="1" t="str">
-        <v>모트모트 일반</v>
+        <v>루카랩컴퍼니 특가</v>
       </c>
       <c r="G113" s="1">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="H113" s="1" t="str">
         <v/>
       </c>
       <c r="I113" s="1">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="J113" s="1">
-        <v>0.2204</v>
+        <v>0.2386</v>
       </c>
     </row>
     <row r="114">
@@ -34990,31 +35291,31 @@
         <v>113</v>
       </c>
       <c r="B114" s="1" t="str">
-        <v>0803791</v>
+        <v>0803303</v>
       </c>
       <c r="C114" s="1" t="str">
-        <v>공장</v>
+        <v>이투컬렉션</v>
       </c>
       <c r="D114" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E114" s="1" t="str">
-        <v>IC0379101</v>
+        <v>IC0330300</v>
       </c>
       <c r="F114" s="1" t="str">
-        <v>공장 대표상품</v>
+        <v>이투컬렉션 일반</v>
       </c>
       <c r="G114" s="1">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="H114" s="1" t="str">
         <v/>
       </c>
       <c r="I114" s="1">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="J114" s="1">
-        <v>0.1763</v>
+        <v>0.2386</v>
       </c>
     </row>
     <row r="115">
@@ -35022,31 +35323,31 @@
         <v>114</v>
       </c>
       <c r="B115" s="1" t="str">
-        <v>0803791</v>
+        <v>0816312</v>
       </c>
       <c r="C115" s="1" t="str">
-        <v>공장</v>
+        <v>엠젯패밀리</v>
       </c>
       <c r="D115" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E115" s="1" t="str">
-        <v>IC0379102</v>
+        <v>IC0631201</v>
       </c>
       <c r="F115" s="1" t="str">
-        <v>공장 특가</v>
+        <v>엠젯패밀리 PB</v>
       </c>
       <c r="G115" s="1">
-        <v>80000</v>
-      </c>
-      <c r="H115" s="1" t="str">
-        <v/>
+        <v>130000</v>
+      </c>
+      <c r="H115" s="1">
+        <v>20000</v>
       </c>
       <c r="I115" s="1">
-        <v>80000</v>
+        <v>110000</v>
       </c>
       <c r="J115" s="1">
-        <v>0.1763</v>
+        <v>0.2187</v>
       </c>
     </row>
     <row r="116">
@@ -35054,31 +35355,31 @@
         <v>115</v>
       </c>
       <c r="B116" s="1" t="str">
-        <v>0803791</v>
+        <v>0816312</v>
       </c>
       <c r="C116" s="1" t="str">
-        <v>공장</v>
+        <v>엠젯패밀리</v>
       </c>
       <c r="D116" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E116" s="1" t="str">
-        <v>IC0379103</v>
+        <v>IC0631202</v>
       </c>
       <c r="F116" s="1" t="str">
-        <v>공장 문구행사</v>
+        <v>엠젯패밀리 리미티드</v>
       </c>
       <c r="G116" s="1">
-        <v>80000</v>
-      </c>
-      <c r="H116" s="1" t="str">
-        <v/>
+        <v>130000</v>
+      </c>
+      <c r="H116" s="1">
+        <v>20000</v>
       </c>
       <c r="I116" s="1">
-        <v>80000</v>
+        <v>110000</v>
       </c>
       <c r="J116" s="1">
-        <v>0.1763</v>
+        <v>0.2187</v>
       </c>
     </row>
     <row r="117">
@@ -35086,31 +35387,31 @@
         <v>116</v>
       </c>
       <c r="B117" s="1" t="str">
-        <v>0803791</v>
+        <v>0807497</v>
       </c>
       <c r="C117" s="1" t="str">
-        <v>공장</v>
+        <v>학산문화사</v>
       </c>
       <c r="D117" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E117" s="1" t="str">
-        <v>IC0379104</v>
+        <v>IC0749701</v>
       </c>
       <c r="F117" s="1" t="str">
-        <v>공장 정품</v>
+        <v>학산문화사 베이직</v>
       </c>
       <c r="G117" s="1">
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="H117" s="1" t="str">
         <v/>
       </c>
       <c r="I117" s="1">
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="J117" s="1">
-        <v>0.1763</v>
+        <v>0.1988</v>
       </c>
     </row>
     <row r="118">
@@ -35118,31 +35419,31 @@
         <v>117</v>
       </c>
       <c r="B118" s="1" t="str">
-        <v>0803741</v>
+        <v>0812988</v>
       </c>
       <c r="C118" s="1" t="str">
-        <v>BST</v>
+        <v>모트모트</v>
       </c>
       <c r="D118" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E118" s="1" t="str">
-        <v>IC0374101</v>
+        <v>IC0298800</v>
       </c>
       <c r="F118" s="1" t="str">
-        <v>BST 베이직</v>
+        <v>모트모트 일반</v>
       </c>
       <c r="G118" s="1">
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="H118" s="1" t="str">
         <v/>
       </c>
       <c r="I118" s="1">
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="J118" s="1">
-        <v>0.1763</v>
+        <v>0.1988</v>
       </c>
     </row>
     <row r="119">
@@ -35150,19 +35451,19 @@
         <v>118</v>
       </c>
       <c r="B119" s="1" t="str">
-        <v>0803741</v>
+        <v>0803791</v>
       </c>
       <c r="C119" s="1" t="str">
-        <v>BST</v>
+        <v>공장</v>
       </c>
       <c r="D119" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E119" s="1" t="str">
-        <v>IC0374102</v>
+        <v>IC0379101</v>
       </c>
       <c r="F119" s="1" t="str">
-        <v>BST PB</v>
+        <v>공장 대표상품</v>
       </c>
       <c r="G119" s="1">
         <v>80000</v>
@@ -35174,7 +35475,7 @@
         <v>80000</v>
       </c>
       <c r="J119" s="1">
-        <v>0.1763</v>
+        <v>0.1591</v>
       </c>
     </row>
     <row r="120">
@@ -35182,19 +35483,19 @@
         <v>119</v>
       </c>
       <c r="B120" s="1" t="str">
-        <v>0803741</v>
+        <v>0803791</v>
       </c>
       <c r="C120" s="1" t="str">
-        <v>BST</v>
+        <v>공장</v>
       </c>
       <c r="D120" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E120" s="1" t="str">
-        <v>IC0374103</v>
+        <v>IC0379102</v>
       </c>
       <c r="F120" s="1" t="str">
-        <v>BST 리미티드</v>
+        <v>공장 특가</v>
       </c>
       <c r="G120" s="1">
         <v>80000</v>
@@ -35206,7 +35507,7 @@
         <v>80000</v>
       </c>
       <c r="J120" s="1">
-        <v>0.1763</v>
+        <v>0.1591</v>
       </c>
     </row>
     <row r="121">
@@ -35214,19 +35515,19 @@
         <v>120</v>
       </c>
       <c r="B121" s="1" t="str">
-        <v>0803741</v>
+        <v>0803791</v>
       </c>
       <c r="C121" s="1" t="str">
-        <v>BST</v>
+        <v>공장</v>
       </c>
       <c r="D121" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E121" s="1" t="str">
-        <v>IC0374104</v>
+        <v>IC0379103</v>
       </c>
       <c r="F121" s="1" t="str">
-        <v>BST 기획전</v>
+        <v>공장 문구행사</v>
       </c>
       <c r="G121" s="1">
         <v>80000</v>
@@ -35238,7 +35539,7 @@
         <v>80000</v>
       </c>
       <c r="J121" s="1">
-        <v>0.1763</v>
+        <v>0.1591</v>
       </c>
     </row>
     <row r="122">
@@ -35246,31 +35547,31 @@
         <v>121</v>
       </c>
       <c r="B122" s="1" t="str">
-        <v>0806798</v>
+        <v>0803791</v>
       </c>
       <c r="C122" s="1" t="str">
-        <v>이가라인유통</v>
+        <v>공장</v>
       </c>
       <c r="D122" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E122" s="1" t="str">
-        <v>IC0679801</v>
+        <v>IC0379104</v>
       </c>
       <c r="F122" s="1" t="str">
-        <v>이가라인유통 기획전</v>
+        <v>공장 정품</v>
       </c>
       <c r="G122" s="1">
-        <v>70000</v>
+        <v>80000</v>
       </c>
       <c r="H122" s="1" t="str">
         <v/>
       </c>
       <c r="I122" s="1">
-        <v>70000</v>
+        <v>80000</v>
       </c>
       <c r="J122" s="1">
-        <v>0.1543</v>
+        <v>0.1591</v>
       </c>
     </row>
     <row r="123">
@@ -35278,31 +35579,31 @@
         <v>122</v>
       </c>
       <c r="B123" s="1" t="str">
-        <v>0806798</v>
+        <v>0803741</v>
       </c>
       <c r="C123" s="1" t="str">
-        <v>이가라인유통</v>
+        <v>BST</v>
       </c>
       <c r="D123" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E123" s="1" t="str">
-        <v>IC0679802</v>
+        <v>IC0374101</v>
       </c>
       <c r="F123" s="1" t="str">
-        <v>이가라인유통 증정</v>
+        <v>BST 베이직</v>
       </c>
       <c r="G123" s="1">
-        <v>70000</v>
+        <v>80000</v>
       </c>
       <c r="H123" s="1" t="str">
         <v/>
       </c>
       <c r="I123" s="1">
-        <v>70000</v>
+        <v>80000</v>
       </c>
       <c r="J123" s="1">
-        <v>0.1543</v>
+        <v>0.1591</v>
       </c>
     </row>
     <row r="124">
@@ -35310,31 +35611,31 @@
         <v>123</v>
       </c>
       <c r="B124" s="1" t="str">
-        <v>0806798</v>
+        <v>0803741</v>
       </c>
       <c r="C124" s="1" t="str">
-        <v>이가라인유통</v>
+        <v>BST</v>
       </c>
       <c r="D124" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E124" s="1" t="str">
-        <v>IC0679803</v>
+        <v>IC0374102</v>
       </c>
       <c r="F124" s="1" t="str">
-        <v>이가라인유통 대표상품</v>
+        <v>BST PB</v>
       </c>
       <c r="G124" s="1">
-        <v>70000</v>
+        <v>80000</v>
       </c>
       <c r="H124" s="1" t="str">
         <v/>
       </c>
       <c r="I124" s="1">
-        <v>70000</v>
+        <v>80000</v>
       </c>
       <c r="J124" s="1">
-        <v>0.1543</v>
+        <v>0.1591</v>
       </c>
     </row>
     <row r="125">
@@ -35342,31 +35643,31 @@
         <v>124</v>
       </c>
       <c r="B125" s="1" t="str">
-        <v>0806798</v>
+        <v>0803741</v>
       </c>
       <c r="C125" s="1" t="str">
-        <v>이가라인유통</v>
+        <v>BST</v>
       </c>
       <c r="D125" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E125" s="1" t="str">
-        <v>IC0679804</v>
+        <v>IC0374103</v>
       </c>
       <c r="F125" s="1" t="str">
-        <v>이가라인유통 특가</v>
+        <v>BST 리미티드</v>
       </c>
       <c r="G125" s="1">
-        <v>70000</v>
+        <v>80000</v>
       </c>
       <c r="H125" s="1" t="str">
         <v/>
       </c>
       <c r="I125" s="1">
-        <v>70000</v>
+        <v>80000</v>
       </c>
       <c r="J125" s="1">
-        <v>0.1543</v>
+        <v>0.1591</v>
       </c>
     </row>
     <row r="126">
@@ -35374,31 +35675,31 @@
         <v>125</v>
       </c>
       <c r="B126" s="1" t="str">
-        <v>01B0504</v>
+        <v>0803741</v>
       </c>
       <c r="C126" s="1" t="str">
-        <v>카카오엔터테인먼트</v>
+        <v>BST</v>
       </c>
       <c r="D126" s="1" t="str">
-        <v>음반</v>
+        <v>문구</v>
       </c>
       <c r="E126" s="1" t="str">
-        <v>IB0050401</v>
+        <v>IC0374104</v>
       </c>
       <c r="F126" s="1" t="str">
-        <v>카카오엔터테인먼트 음반</v>
+        <v>BST 기획전</v>
       </c>
       <c r="G126" s="1">
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="H126" s="1" t="str">
         <v/>
       </c>
       <c r="I126" s="1">
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="J126" s="1">
-        <v>0.1322</v>
+        <v>0.1591</v>
       </c>
     </row>
     <row r="127">
@@ -35406,31 +35707,31 @@
         <v>126</v>
       </c>
       <c r="B127" s="1" t="str">
-        <v>01B0504</v>
+        <v>0806798</v>
       </c>
       <c r="C127" s="1" t="str">
-        <v>카카오엔터테인먼트</v>
+        <v>이가라인유통</v>
       </c>
       <c r="D127" s="1" t="str">
-        <v>음반</v>
+        <v>문구</v>
       </c>
       <c r="E127" s="1" t="str">
-        <v>IB0050402</v>
+        <v>IC0679801</v>
       </c>
       <c r="F127" s="1" t="str">
-        <v>카카오엔터테인먼트 KPOP</v>
+        <v>이가라인유통 기획전</v>
       </c>
       <c r="G127" s="1">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="H127" s="1" t="str">
         <v/>
       </c>
       <c r="I127" s="1">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="J127" s="1">
-        <v>0.1322</v>
+        <v>0.1392</v>
       </c>
     </row>
     <row r="128">
@@ -35438,31 +35739,31 @@
         <v>127</v>
       </c>
       <c r="B128" s="1" t="str">
-        <v>01B0504</v>
+        <v>0806798</v>
       </c>
       <c r="C128" s="1" t="str">
-        <v>카카오엔터테인먼트</v>
+        <v>이가라인유통</v>
       </c>
       <c r="D128" s="1" t="str">
-        <v>음반</v>
+        <v>문구</v>
       </c>
       <c r="E128" s="1" t="str">
-        <v>IB0050403</v>
+        <v>IC0679802</v>
       </c>
       <c r="F128" s="1" t="str">
-        <v>카카오엔터테인먼트 해외음반</v>
+        <v>이가라인유통 증정</v>
       </c>
       <c r="G128" s="1">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="H128" s="1" t="str">
         <v/>
       </c>
       <c r="I128" s="1">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="J128" s="1">
-        <v>0.1322</v>
+        <v>0.1392</v>
       </c>
     </row>
     <row r="129">
@@ -35470,31 +35771,31 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="str">
-        <v>01B0478</v>
+        <v>0806798</v>
       </c>
       <c r="C129" s="1" t="str">
-        <v>와이지플러스</v>
+        <v>이가라인유통</v>
       </c>
       <c r="D129" s="1" t="str">
-        <v>음반</v>
+        <v>문구</v>
       </c>
       <c r="E129" s="1" t="str">
-        <v>IB0047801</v>
+        <v>IC0679803</v>
       </c>
       <c r="F129" s="1" t="str">
-        <v>와이지플러스 KPOP</v>
+        <v>이가라인유통 대표상품</v>
       </c>
       <c r="G129" s="1">
-        <v>50000</v>
+        <v>70000</v>
       </c>
       <c r="H129" s="1" t="str">
         <v/>
       </c>
       <c r="I129" s="1">
-        <v>50000</v>
+        <v>70000</v>
       </c>
       <c r="J129" s="1">
-        <v>0.1102</v>
+        <v>0.1392</v>
       </c>
     </row>
     <row r="130">
@@ -35502,31 +35803,31 @@
         <v>129</v>
       </c>
       <c r="B130" s="1" t="str">
-        <v>01B0478</v>
+        <v>0806798</v>
       </c>
       <c r="C130" s="1" t="str">
-        <v>와이지플러스</v>
+        <v>이가라인유통</v>
       </c>
       <c r="D130" s="1" t="str">
-        <v>음반</v>
+        <v>문구</v>
       </c>
       <c r="E130" s="1" t="str">
-        <v>IB0047802</v>
+        <v>IC0679804</v>
       </c>
       <c r="F130" s="1" t="str">
-        <v>와이지플러스 해외음반</v>
+        <v>이가라인유통 특가</v>
       </c>
       <c r="G130" s="1">
-        <v>50000</v>
+        <v>70000</v>
       </c>
       <c r="H130" s="1" t="str">
         <v/>
       </c>
       <c r="I130" s="1">
-        <v>50000</v>
+        <v>70000</v>
       </c>
       <c r="J130" s="1">
-        <v>0.1102</v>
+        <v>0.1392</v>
       </c>
     </row>
     <row r="131">
@@ -35534,31 +35835,31 @@
         <v>130</v>
       </c>
       <c r="B131" s="1" t="str">
-        <v>01B0478</v>
+        <v>01B0504</v>
       </c>
       <c r="C131" s="1" t="str">
-        <v>와이지플러스</v>
+        <v>카카오엔터테인먼트</v>
       </c>
       <c r="D131" s="1" t="str">
         <v>음반</v>
       </c>
       <c r="E131" s="1" t="str">
-        <v>IB0047803</v>
+        <v>IB0050401</v>
       </c>
       <c r="F131" s="1" t="str">
-        <v>와이지플러스 음반</v>
+        <v>카카오엔터테인먼트 음반</v>
       </c>
       <c r="G131" s="1">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="H131" s="1" t="str">
         <v/>
       </c>
       <c r="I131" s="1">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="J131" s="1">
-        <v>0.1102</v>
+        <v>0.1193</v>
       </c>
     </row>
     <row r="132">
@@ -35566,31 +35867,31 @@
         <v>131</v>
       </c>
       <c r="B132" s="1" t="str">
-        <v>0816166</v>
+        <v>01B0504</v>
       </c>
       <c r="C132" s="1" t="str">
-        <v>해밀</v>
+        <v>카카오엔터테인먼트</v>
       </c>
       <c r="D132" s="1" t="str">
-        <v>문구</v>
+        <v>음반</v>
       </c>
       <c r="E132" s="1" t="str">
-        <v>IC0616601</v>
+        <v>IB0050402</v>
       </c>
       <c r="F132" s="1" t="str">
-        <v>해밀 정품</v>
+        <v>카카오엔터테인먼트 KPOP</v>
       </c>
       <c r="G132" s="1">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="H132" s="1" t="str">
         <v/>
       </c>
       <c r="I132" s="1">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="J132" s="1">
-        <v>0.0882</v>
+        <v>0.1193</v>
       </c>
     </row>
     <row r="133">
@@ -35598,31 +35899,31 @@
         <v>132</v>
       </c>
       <c r="B133" s="1" t="str">
-        <v>0816166</v>
+        <v>01B0504</v>
       </c>
       <c r="C133" s="1" t="str">
-        <v>해밀</v>
+        <v>카카오엔터테인먼트</v>
       </c>
       <c r="D133" s="1" t="str">
-        <v>문구</v>
+        <v>음반</v>
       </c>
       <c r="E133" s="1" t="str">
-        <v>IC0616602</v>
+        <v>IB0050403</v>
       </c>
       <c r="F133" s="1" t="str">
-        <v>해밀 베이직</v>
+        <v>카카오엔터테인먼트 해외음반</v>
       </c>
       <c r="G133" s="1">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="H133" s="1" t="str">
         <v/>
       </c>
       <c r="I133" s="1">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="J133" s="1">
-        <v>0.0882</v>
+        <v>0.1193</v>
       </c>
     </row>
     <row r="134">
@@ -35630,31 +35931,31 @@
         <v>133</v>
       </c>
       <c r="B134" s="1" t="str">
-        <v>0816166</v>
+        <v>01B0478</v>
       </c>
       <c r="C134" s="1" t="str">
-        <v>해밀</v>
+        <v>와이지플러스</v>
       </c>
       <c r="D134" s="1" t="str">
-        <v>문구</v>
+        <v>음반</v>
       </c>
       <c r="E134" s="1" t="str">
-        <v>IC0616603</v>
+        <v>IB0047801</v>
       </c>
       <c r="F134" s="1" t="str">
-        <v>해밀 PB</v>
+        <v>와이지플러스 KPOP</v>
       </c>
       <c r="G134" s="1">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="H134" s="1" t="str">
         <v/>
       </c>
       <c r="I134" s="1">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="J134" s="1">
-        <v>0.0882</v>
+        <v>0.0994</v>
       </c>
     </row>
     <row r="135">
@@ -35662,31 +35963,31 @@
         <v>134</v>
       </c>
       <c r="B135" s="1" t="str">
-        <v>0816166</v>
+        <v>01B0478</v>
       </c>
       <c r="C135" s="1" t="str">
-        <v>해밀</v>
+        <v>와이지플러스</v>
       </c>
       <c r="D135" s="1" t="str">
-        <v>문구</v>
+        <v>음반</v>
       </c>
       <c r="E135" s="1" t="str">
-        <v>IC0616604</v>
+        <v>IB0047802</v>
       </c>
       <c r="F135" s="1" t="str">
-        <v>해밀 리미티드</v>
+        <v>와이지플러스 해외음반</v>
       </c>
       <c r="G135" s="1">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="H135" s="1" t="str">
         <v/>
       </c>
       <c r="I135" s="1">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="J135" s="1">
-        <v>0.0882</v>
+        <v>0.0994</v>
       </c>
     </row>
     <row r="136">
@@ -35694,31 +35995,31 @@
         <v>135</v>
       </c>
       <c r="B136" s="1" t="str">
-        <v>0800334</v>
+        <v>01B0478</v>
       </c>
       <c r="C136" s="1" t="str">
-        <v>아이비스코리아</v>
+        <v>와이지플러스</v>
       </c>
       <c r="D136" s="1" t="str">
-        <v>문구</v>
+        <v>음반</v>
       </c>
       <c r="E136" s="1" t="str">
-        <v>IC0033401</v>
+        <v>IB0047803</v>
       </c>
       <c r="F136" s="1" t="str">
-        <v>아이비스코리아 PB</v>
+        <v>와이지플러스 음반</v>
       </c>
       <c r="G136" s="1">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="H136" s="1" t="str">
         <v/>
       </c>
       <c r="I136" s="1">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="J136" s="1">
-        <v>0.0661</v>
+        <v>0.0994</v>
       </c>
     </row>
     <row r="137">
@@ -35726,31 +36027,31 @@
         <v>136</v>
       </c>
       <c r="B137" s="1" t="str">
-        <v>0800334</v>
+        <v>0816166</v>
       </c>
       <c r="C137" s="1" t="str">
-        <v>아이비스코리아</v>
+        <v>해밀</v>
       </c>
       <c r="D137" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E137" s="1" t="str">
-        <v>IC0033402</v>
+        <v>IC0616601</v>
       </c>
       <c r="F137" s="1" t="str">
-        <v>아이비스코리아 리미티드</v>
+        <v>해밀 정품</v>
       </c>
       <c r="G137" s="1">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="H137" s="1" t="str">
         <v/>
       </c>
       <c r="I137" s="1">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="J137" s="1">
-        <v>0.0661</v>
+        <v>0.0795</v>
       </c>
     </row>
     <row r="138">
@@ -35758,31 +36059,31 @@
         <v>137</v>
       </c>
       <c r="B138" s="1" t="str">
-        <v>0800334</v>
+        <v>0816166</v>
       </c>
       <c r="C138" s="1" t="str">
-        <v>아이비스코리아</v>
+        <v>해밀</v>
       </c>
       <c r="D138" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E138" s="1" t="str">
-        <v>IC0033403</v>
+        <v>IC0616602</v>
       </c>
       <c r="F138" s="1" t="str">
-        <v>아이비스코리아 기획전</v>
+        <v>해밀 베이직</v>
       </c>
       <c r="G138" s="1">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="H138" s="1" t="str">
         <v/>
       </c>
       <c r="I138" s="1">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="J138" s="1">
-        <v>0.0661</v>
+        <v>0.0795</v>
       </c>
     </row>
     <row r="139">
@@ -35790,31 +36091,31 @@
         <v>138</v>
       </c>
       <c r="B139" s="1" t="str">
-        <v>0800334</v>
+        <v>0816166</v>
       </c>
       <c r="C139" s="1" t="str">
-        <v>아이비스코리아</v>
+        <v>해밀</v>
       </c>
       <c r="D139" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E139" s="1" t="str">
-        <v>IC0033404</v>
+        <v>IC0616603</v>
       </c>
       <c r="F139" s="1" t="str">
-        <v>아이비스코리아 증정</v>
+        <v>해밀 PB</v>
       </c>
       <c r="G139" s="1">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="H139" s="1" t="str">
         <v/>
       </c>
       <c r="I139" s="1">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="J139" s="1">
-        <v>0.0661</v>
+        <v>0.0795</v>
       </c>
     </row>
     <row r="140">
@@ -35822,31 +36123,31 @@
         <v>139</v>
       </c>
       <c r="B140" s="1" t="str">
-        <v>0807485</v>
+        <v>0816166</v>
       </c>
       <c r="C140" s="1" t="str">
-        <v>대시앤도트</v>
+        <v>해밀</v>
       </c>
       <c r="D140" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E140" s="1" t="str">
-        <v>IC0748501</v>
+        <v>IC0616604</v>
       </c>
       <c r="F140" s="1" t="str">
-        <v>대시앤도트 기획전</v>
+        <v>해밀 리미티드</v>
       </c>
       <c r="G140" s="1">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="H140" s="1" t="str">
         <v/>
       </c>
       <c r="I140" s="1">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="J140" s="1">
-        <v>0.0661</v>
+        <v>0.0795</v>
       </c>
     </row>
     <row r="141">
@@ -35854,19 +36155,19 @@
         <v>140</v>
       </c>
       <c r="B141" s="1" t="str">
-        <v>0807485</v>
+        <v>0800334</v>
       </c>
       <c r="C141" s="1" t="str">
-        <v>대시앤도트</v>
+        <v>아이비스코리아</v>
       </c>
       <c r="D141" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E141" s="1" t="str">
-        <v>IC0748502</v>
+        <v>IC0033401</v>
       </c>
       <c r="F141" s="1" t="str">
-        <v>대시앤도트 증정</v>
+        <v>아이비스코리아 PB</v>
       </c>
       <c r="G141" s="1">
         <v>30000</v>
@@ -35878,7 +36179,7 @@
         <v>30000</v>
       </c>
       <c r="J141" s="1">
-        <v>0.0661</v>
+        <v>0.0596</v>
       </c>
     </row>
     <row r="142">
@@ -35886,19 +36187,19 @@
         <v>141</v>
       </c>
       <c r="B142" s="1" t="str">
-        <v>0807485</v>
+        <v>0800334</v>
       </c>
       <c r="C142" s="1" t="str">
-        <v>대시앤도트</v>
+        <v>아이비스코리아</v>
       </c>
       <c r="D142" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E142" s="1" t="str">
-        <v>IC0748503</v>
+        <v>IC0033402</v>
       </c>
       <c r="F142" s="1" t="str">
-        <v>대시앤도트 대표상품</v>
+        <v>아이비스코리아 리미티드</v>
       </c>
       <c r="G142" s="1">
         <v>30000</v>
@@ -35910,7 +36211,7 @@
         <v>30000</v>
       </c>
       <c r="J142" s="1">
-        <v>0.0661</v>
+        <v>0.0596</v>
       </c>
     </row>
     <row r="143">
@@ -35918,19 +36219,19 @@
         <v>142</v>
       </c>
       <c r="B143" s="1" t="str">
-        <v>0807481</v>
+        <v>0800334</v>
       </c>
       <c r="C143" s="1" t="str">
-        <v>골드디자인</v>
+        <v>아이비스코리아</v>
       </c>
       <c r="D143" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E143" s="1" t="str">
-        <v>IC0748101</v>
+        <v>IC0033403</v>
       </c>
       <c r="F143" s="1" t="str">
-        <v>골드디자인 리미티드</v>
+        <v>아이비스코리아 기획전</v>
       </c>
       <c r="G143" s="1">
         <v>30000</v>
@@ -35942,7 +36243,7 @@
         <v>30000</v>
       </c>
       <c r="J143" s="1">
-        <v>0.0661</v>
+        <v>0.0596</v>
       </c>
     </row>
     <row r="144">
@@ -35950,19 +36251,19 @@
         <v>143</v>
       </c>
       <c r="B144" s="1" t="str">
-        <v>0807481</v>
+        <v>0800334</v>
       </c>
       <c r="C144" s="1" t="str">
-        <v>골드디자인</v>
+        <v>아이비스코리아</v>
       </c>
       <c r="D144" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E144" s="1" t="str">
-        <v>IC0748102</v>
+        <v>IC0033404</v>
       </c>
       <c r="F144" s="1" t="str">
-        <v>골드디자인 기획전</v>
+        <v>아이비스코리아 증정</v>
       </c>
       <c r="G144" s="1">
         <v>30000</v>
@@ -35974,7 +36275,7 @@
         <v>30000</v>
       </c>
       <c r="J144" s="1">
-        <v>0.0661</v>
+        <v>0.0596</v>
       </c>
     </row>
     <row r="145">
@@ -35982,19 +36283,19 @@
         <v>144</v>
       </c>
       <c r="B145" s="1" t="str">
-        <v>0807481</v>
+        <v>0807485</v>
       </c>
       <c r="C145" s="1" t="str">
-        <v>골드디자인</v>
+        <v>대시앤도트</v>
       </c>
       <c r="D145" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E145" s="1" t="str">
-        <v>IC0748103</v>
+        <v>IC0748501</v>
       </c>
       <c r="F145" s="1" t="str">
-        <v>골드디자인 증정</v>
+        <v>대시앤도트 기획전</v>
       </c>
       <c r="G145" s="1">
         <v>30000</v>
@@ -36006,7 +36307,7 @@
         <v>30000</v>
       </c>
       <c r="J145" s="1">
-        <v>0.0661</v>
+        <v>0.0596</v>
       </c>
     </row>
     <row r="146">
@@ -36014,19 +36315,19 @@
         <v>145</v>
       </c>
       <c r="B146" s="1" t="str">
-        <v>0807481</v>
+        <v>0807485</v>
       </c>
       <c r="C146" s="1" t="str">
-        <v>골드디자인</v>
+        <v>대시앤도트</v>
       </c>
       <c r="D146" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E146" s="1" t="str">
-        <v>IC0748104</v>
+        <v>IC0748502</v>
       </c>
       <c r="F146" s="1" t="str">
-        <v>골드디자인 대표상품</v>
+        <v>대시앤도트 증정</v>
       </c>
       <c r="G146" s="1">
         <v>30000</v>
@@ -36038,7 +36339,7 @@
         <v>30000</v>
       </c>
       <c r="J146" s="1">
-        <v>0.0661</v>
+        <v>0.0596</v>
       </c>
     </row>
     <row r="147">
@@ -36046,19 +36347,19 @@
         <v>146</v>
       </c>
       <c r="B147" s="1" t="str">
-        <v>0803303</v>
+        <v>0807485</v>
       </c>
       <c r="C147" s="1" t="str">
-        <v>이투컬렉션</v>
+        <v>대시앤도트</v>
       </c>
       <c r="D147" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E147" s="1" t="str">
-        <v>IC0330301</v>
+        <v>IC0748503</v>
       </c>
       <c r="F147" s="1" t="str">
-        <v>이투컬렉션 기획전</v>
+        <v>대시앤도트 대표상품</v>
       </c>
       <c r="G147" s="1">
         <v>30000</v>
@@ -36070,7 +36371,7 @@
         <v>30000</v>
       </c>
       <c r="J147" s="1">
-        <v>0.0661</v>
+        <v>0.0596</v>
       </c>
     </row>
     <row r="148">
@@ -36078,19 +36379,19 @@
         <v>147</v>
       </c>
       <c r="B148" s="1" t="str">
-        <v>0803303</v>
+        <v>0807481</v>
       </c>
       <c r="C148" s="1" t="str">
-        <v>이투컬렉션</v>
+        <v>골드디자인</v>
       </c>
       <c r="D148" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E148" s="1" t="str">
-        <v>IC0330302</v>
+        <v>IC0748101</v>
       </c>
       <c r="F148" s="1" t="str">
-        <v>이투컬렉션 증정</v>
+        <v>골드디자인 리미티드</v>
       </c>
       <c r="G148" s="1">
         <v>30000</v>
@@ -36102,7 +36403,7 @@
         <v>30000</v>
       </c>
       <c r="J148" s="1">
-        <v>0.0661</v>
+        <v>0.0596</v>
       </c>
     </row>
     <row r="149">
@@ -36110,19 +36411,19 @@
         <v>148</v>
       </c>
       <c r="B149" s="1" t="str">
-        <v>0803303</v>
+        <v>0807481</v>
       </c>
       <c r="C149" s="1" t="str">
-        <v>이투컬렉션</v>
+        <v>골드디자인</v>
       </c>
       <c r="D149" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E149" s="1" t="str">
-        <v>IC0330303</v>
+        <v>IC0748102</v>
       </c>
       <c r="F149" s="1" t="str">
-        <v>이투컬렉션 대표상품</v>
+        <v>골드디자인 기획전</v>
       </c>
       <c r="G149" s="1">
         <v>30000</v>
@@ -36134,7 +36435,7 @@
         <v>30000</v>
       </c>
       <c r="J149" s="1">
-        <v>0.0661</v>
+        <v>0.0596</v>
       </c>
     </row>
     <row r="150">
@@ -36142,19 +36443,19 @@
         <v>149</v>
       </c>
       <c r="B150" s="1" t="str">
-        <v>0812988</v>
+        <v>0807481</v>
       </c>
       <c r="C150" s="1" t="str">
-        <v>모트모트</v>
+        <v>골드디자인</v>
       </c>
       <c r="D150" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E150" s="1" t="str">
-        <v>IC0298801</v>
+        <v>IC0748103</v>
       </c>
       <c r="F150" s="1" t="str">
-        <v>모트모트 PB</v>
+        <v>골드디자인 증정</v>
       </c>
       <c r="G150" s="1">
         <v>30000</v>
@@ -36166,7 +36467,7 @@
         <v>30000</v>
       </c>
       <c r="J150" s="1">
-        <v>0.0661</v>
+        <v>0.0596</v>
       </c>
     </row>
     <row r="151">
@@ -36174,19 +36475,19 @@
         <v>150</v>
       </c>
       <c r="B151" s="1" t="str">
-        <v>0812988</v>
+        <v>0807481</v>
       </c>
       <c r="C151" s="1" t="str">
-        <v>모트모트</v>
+        <v>골드디자인</v>
       </c>
       <c r="D151" s="1" t="str">
         <v>문구</v>
       </c>
       <c r="E151" s="1" t="str">
-        <v>IC0298802</v>
+        <v>IC0748104</v>
       </c>
       <c r="F151" s="1" t="str">
-        <v>모트모트 리미티드</v>
+        <v>골드디자인 대표상품</v>
       </c>
       <c r="G151" s="1">
         <v>30000</v>
@@ -36198,12 +36499,172 @@
         <v>30000</v>
       </c>
       <c r="J151" s="1">
-        <v>0.0661</v>
+        <v>0.0596</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152" s="1" t="str">
+        <v>0803303</v>
+      </c>
+      <c r="C152" s="1" t="str">
+        <v>이투컬렉션</v>
+      </c>
+      <c r="D152" s="1" t="str">
+        <v>문구</v>
+      </c>
+      <c r="E152" s="1" t="str">
+        <v>IC0330301</v>
+      </c>
+      <c r="F152" s="1" t="str">
+        <v>이투컬렉션 기획전</v>
+      </c>
+      <c r="G152" s="1">
+        <v>30000</v>
+      </c>
+      <c r="H152" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I152" s="1">
+        <v>30000</v>
+      </c>
+      <c r="J152" s="1">
+        <v>0.0596</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153" s="1" t="str">
+        <v>0803303</v>
+      </c>
+      <c r="C153" s="1" t="str">
+        <v>이투컬렉션</v>
+      </c>
+      <c r="D153" s="1" t="str">
+        <v>문구</v>
+      </c>
+      <c r="E153" s="1" t="str">
+        <v>IC0330302</v>
+      </c>
+      <c r="F153" s="1" t="str">
+        <v>이투컬렉션 증정</v>
+      </c>
+      <c r="G153" s="1">
+        <v>30000</v>
+      </c>
+      <c r="H153" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I153" s="1">
+        <v>30000</v>
+      </c>
+      <c r="J153" s="1">
+        <v>0.0596</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154" s="1" t="str">
+        <v>0803303</v>
+      </c>
+      <c r="C154" s="1" t="str">
+        <v>이투컬렉션</v>
+      </c>
+      <c r="D154" s="1" t="str">
+        <v>문구</v>
+      </c>
+      <c r="E154" s="1" t="str">
+        <v>IC0330303</v>
+      </c>
+      <c r="F154" s="1" t="str">
+        <v>이투컬렉션 대표상품</v>
+      </c>
+      <c r="G154" s="1">
+        <v>30000</v>
+      </c>
+      <c r="H154" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I154" s="1">
+        <v>30000</v>
+      </c>
+      <c r="J154" s="1">
+        <v>0.0596</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155" s="1" t="str">
+        <v>0812988</v>
+      </c>
+      <c r="C155" s="1" t="str">
+        <v>모트모트</v>
+      </c>
+      <c r="D155" s="1" t="str">
+        <v>문구</v>
+      </c>
+      <c r="E155" s="1" t="str">
+        <v>IC0298801</v>
+      </c>
+      <c r="F155" s="1" t="str">
+        <v>모트모트 PB</v>
+      </c>
+      <c r="G155" s="1">
+        <v>30000</v>
+      </c>
+      <c r="H155" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I155" s="1">
+        <v>30000</v>
+      </c>
+      <c r="J155" s="1">
+        <v>0.0596</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156" s="1" t="str">
+        <v>0812988</v>
+      </c>
+      <c r="C156" s="1" t="str">
+        <v>모트모트</v>
+      </c>
+      <c r="D156" s="1" t="str">
+        <v>문구</v>
+      </c>
+      <c r="E156" s="1" t="str">
+        <v>IC0298802</v>
+      </c>
+      <c r="F156" s="1" t="str">
+        <v>모트모트 리미티드</v>
+      </c>
+      <c r="G156" s="1">
+        <v>30000</v>
+      </c>
+      <c r="H156" s="1" t="str">
+        <v/>
+      </c>
+      <c r="I156" s="1">
+        <v>30000</v>
+      </c>
+      <c r="J156" s="1">
+        <v>0.0596</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J151"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J156"/>
   </ignoredErrors>
 </worksheet>
 </file>